--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45121</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>46175</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45301</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45173</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45678</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45006</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>45742</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>45077</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45926</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45979</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45020</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>46100</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45378</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>46145</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45168</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45168</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>45786</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45908</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>46175</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45072</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>46205</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45008</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>45760</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>45048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>45378</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45484</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>45761</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>44670</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>44991</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         <v>45104</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         <v>45224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>45002</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44595</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>45667</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>45818</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>45125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>45399</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>45959</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>45415</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44600</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>46202</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>45574</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>46215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>46274</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>46238</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>44803</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>45071</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>46073</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44490</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44481</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44614</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44670</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44509</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44480</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44585</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44824</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44785</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44578</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44516</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44862</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44826</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44603</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44483</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44494</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44542</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44512</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>44790</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44530</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44588</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44588</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44790</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44790</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44475</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44670</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44729</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44774</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44733</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>44480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44463</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44588</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>44634</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>44480</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44769</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44612</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>44819</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>44608</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44480</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>44564</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>44636</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>44817</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44676</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44604</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44476</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44854</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44823</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>44854</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>44790</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44620</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>44722</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>44824</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44742</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44851</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>44644</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44621</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>44876</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12556,7 +12556,7 @@
         <v>44470</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44776</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>44634</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>44608</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44466</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44866</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44588</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>44588</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45033</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45196</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45111</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44607</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45624</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45617</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44991</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45114</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45411</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>44903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>44879</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44991</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45048</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44693</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>44981</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44910</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45346</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45732</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45394</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>45052</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45299</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45610</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45623</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45453</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45020</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>44992</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45030</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45224</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>44994</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>45539</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44720</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45237</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45237</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45533</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>45552</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45097</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>45607</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>45674</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44931</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45558</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>44965</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45328</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45309</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44861</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45300</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>45254</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45350</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45063</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45145</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45163</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45187</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44966</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45482</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>44510</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44553</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>44981</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>45217</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45552</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>44566</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44488</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45460</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>44918</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45450</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45275</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45163</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44988</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45168</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45171</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44613</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45187</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45128</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>44769</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45128</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45189</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45650</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45540</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45425</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45041</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45475</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45232</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45482</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>44754</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>44867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45236</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45174</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45121</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>44857</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>44903</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45359</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>44944</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>44944</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45467</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45000</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>45554</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45440</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45257</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45495</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>44999</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45301</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44789</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>44958</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>45219</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         <v>44663</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21283,7 +21283,7 @@
         <v>45041</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45567</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
         <v>45201</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45623</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45086</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>44944</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45330</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21794,7 +21794,7 @@
         <v>45250</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45700</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>44539</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>45225</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
         <v>45299</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44910</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45415</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45559</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22378,7 +22378,7 @@
         <v>44598</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22451,7 +22451,7 @@
         <v>44542</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45224</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44848</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>44599</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>44984</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45245</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22889,7 +22889,7 @@
         <v>45732</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45707</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45884</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>45954</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45881</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>45658</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44578</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45525</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>44964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45121</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>46136</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45211</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45075</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>44630</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>45825</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45371</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45100</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>44795</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>45280</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45891</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         <v>45891</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45112</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>45111</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45891</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>45202</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>45632</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45749</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45245</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>44585</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25021,7 +25021,7 @@
         <v>45875</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45875</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25167,7 +25167,7 @@
         <v>45170</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>46136</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>45901</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25386,7 +25386,7 @@
         <v>45901</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44867</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>44732</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>45635</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>45483</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>45923</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>45924</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>45919</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45805</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>45834</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45632</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>44964</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45713</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45615</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>44832</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44984</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>44984</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45915</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>45018</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26778,7 +26778,7 @@
         <v>45791</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>45915</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>45105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>44788</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45070</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27143,7 +27143,7 @@
         <v>45768</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45028</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>45456</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27362,7 +27362,7 @@
         <v>45481</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>44964</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>45257</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45533</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45533</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45001</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45569</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44879</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45475</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44510</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>44961</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44984</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45090</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45930</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45174</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45091</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>45646</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45934</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45545</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45361</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>44896</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45699</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45114</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45111</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45111</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45098</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45154</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45722</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45481</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45947</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45453</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>44992</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>44502</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45378</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45377</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45219</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45211</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45952</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44977</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45498</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45954</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>44825</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45215</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45959</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45533</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45959</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30745,7 +30745,7 @@
         <v>45959</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45754</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45187</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>44475</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>44839</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45961</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>46150</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>44875</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45533</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>44973</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45106</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>45301</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45722</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>45106</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45743</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45569</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>45148</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45361</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44952</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>45548</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>45394</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45971</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45138</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45317</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>45384</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45513</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45513</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45637</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>46097</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45153</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45635</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45211</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45985</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44890</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45278</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33310,7 +33310,7 @@
         <v>45029</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45588</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45699</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45086</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45128</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46104</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45867</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>44635</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45343</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33967,7 +33967,7 @@
         <v>45581</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>45539</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>45301</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45755</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>45981</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34332,7 +34332,7 @@
         <v>44546</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45369</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45961</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45526</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45741</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45994</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45622</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45574</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45533</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>46002</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>46002</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>44833</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44897</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45498</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45009</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>44992</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>44999</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35593,7 +35593,7 @@
         <v>44999</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35666,7 +35666,7 @@
         <v>45148</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>45581</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45495</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45618</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45699</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36031,7 +36031,7 @@
         <v>46018</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36104,7 +36104,7 @@
         <v>45259</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45259</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45562</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45086</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>46028</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>46028</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>44517</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45533</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>44992</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45121</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>46030</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45275</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37000,7 +37000,7 @@
         <v>46030</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>46034</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>46034</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>44746</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>46035</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>44598</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>46037</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37511,7 +37511,7 @@
         <v>45079</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>46037</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>46175</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37730,7 +37730,7 @@
         <v>44579</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>44495</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37876,7 +37876,7 @@
         <v>46037</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37949,7 +37949,7 @@
         <v>45090</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45090</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>44638</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>46043</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>46043</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38314,7 +38314,7 @@
         <v>46044</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38387,7 +38387,7 @@
         <v>45245</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>45415</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>46174</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38606,7 +38606,7 @@
         <v>46175</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38679,7 +38679,7 @@
         <v>46176</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38752,7 +38752,7 @@
         <v>45621</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>46175</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>46176</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>44861</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45308</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>46176</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>45063</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44895</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>45009</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>44820</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45215</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>45215</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45351</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>46057</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45539</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45565</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45482</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46065</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45195</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45026</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>46181</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45266</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45554</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45632</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44803</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45567</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>44587</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45110</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>46184</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46183</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>46184</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>46184</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46184</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45503</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>46083</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>46083</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44956</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>44596</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41531,7 +41531,7 @@
         <v>45113</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>45666</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41677,7 +41677,7 @@
         <v>44918</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41750,7 +41750,7 @@
         <v>45027</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41828,7 +41828,7 @@
         <v>45224</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>45377</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>46186</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>45114</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>46091</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>46092</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>46092</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>46092</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>46097</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45349</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45985</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45334</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45114</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>46099</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>44600</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>46099</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>45581</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45359</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>44895</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>44587</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>46101</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>46196</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45569</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>45588</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         <v>46196</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>46197</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45355</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43804,7 +43804,7 @@
         <v>46198</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46105</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>44949</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45090</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>44467</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>46197</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>44790</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44784</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46197</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>44935</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>44852</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>46111</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>46112</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>46112</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>45100</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>46112</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>46112</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45517</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>46112</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45221,7 +45221,7 @@
         <v>46112</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45299,7 +45299,7 @@
         <v>46112</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>46112</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45450,7 +45450,7 @@
         <v>46203</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45523,7 +45523,7 @@
         <v>44578</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45596,7 +45596,7 @@
         <v>46113</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>44994</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>44900</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45815,7 +45815,7 @@
         <v>46113</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>45201</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>46113</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>46113</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44966</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>46113</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46253,7 +46253,7 @@
         <v>45323</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46326,7 +46326,7 @@
         <v>45308</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46399,7 +46399,7 @@
         <v>45111</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46472,7 +46472,7 @@
         <v>46121</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>45086</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>45196</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46691,7 +46691,7 @@
         <v>46125</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>46244</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>46128</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46910,7 +46910,7 @@
         <v>45320</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>44987</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47056,7 +47056,7 @@
         <v>46202</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45208</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>45001</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>44585</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47348,7 +47348,7 @@
         <v>45260</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44943</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45371</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>44910</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>44938</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45804</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47791,7 +47791,7 @@
         <v>44949</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47869,7 +47869,7 @@
         <v>45020</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45568</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48015,7 +48015,7 @@
         <v>45992</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>44894</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48161,7 +48161,7 @@
         <v>45224</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45867</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45867</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>45485</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>44790</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>44790</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>45211</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48677,7 +48677,7 @@
         <v>44893</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>46203</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>45174</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>46204</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>44994</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>45176</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49120,7 +49120,7 @@
         <v>45759</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49193,7 +49193,7 @@
         <v>46208</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45061</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>45330</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>45096</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49490,7 +49490,7 @@
         <v>45391</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>46206</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45630</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45110</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>46206</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>45182</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>46253</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45761</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>45128</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>45128</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>44999</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>46210</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>44466</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45530</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>46253</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>46253</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50658,7 +50658,7 @@
         <v>45483</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50731,7 +50731,7 @@
         <v>45271</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50804,7 +50804,7 @@
         <v>46254</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45113</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50950,7 +50950,7 @@
         <v>44540</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>44916</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51096,7 +51096,7 @@
         <v>45149</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45482</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>44879</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>46216</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>46259</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>46216</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>46216</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>46213</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>46256</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45700</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>44603</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>45147</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>44959</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>45897</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45171</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>45113</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>46213</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>44967</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>46256</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52483,7 +52483,7 @@
         <v>46256</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52556,7 +52556,7 @@
         <v>46213</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>44963</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52702,7 +52702,7 @@
         <v>45720</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52775,7 +52775,7 @@
         <v>44909</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>45699</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52921,7 +52921,7 @@
         <v>44784</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>46219</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53067,7 +53067,7 @@
         <v>45243</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53140,7 +53140,7 @@
         <v>44643</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>46219</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>45238</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53359,7 +53359,7 @@
         <v>44893</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>45572</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53505,7 +53505,7 @@
         <v>45147</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53578,7 +53578,7 @@
         <v>45169</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53651,7 +53651,7 @@
         <v>44867</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53724,7 +53724,7 @@
         <v>44745</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45630</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>45533</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53943,7 +53943,7 @@
         <v>45533</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54021,7 +54021,7 @@
         <v>45124</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54094,7 +54094,7 @@
         <v>45071</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54167,7 +54167,7 @@
         <v>45481</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54240,7 +54240,7 @@
         <v>45111</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54313,7 +54313,7 @@
         <v>45391</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54386,7 +54386,7 @@
         <v>46271</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54459,7 +54459,7 @@
         <v>46272</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54532,7 +54532,7 @@
         <v>46230</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54605,7 +54605,7 @@
         <v>46231</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54678,7 +54678,7 @@
         <v>46272</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54751,7 +54751,7 @@
         <v>46272</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54824,7 +54824,7 @@
         <v>46272</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54897,7 +54897,7 @@
         <v>46272</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54970,7 +54970,7 @@
         <v>46272</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>46275</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55116,7 +55116,7 @@
         <v>46275</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55189,7 +55189,7 @@
         <v>46274</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>46232</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>46275</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55408,7 +55408,7 @@
         <v>46274</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55481,7 +55481,7 @@
         <v>46233</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55554,7 +55554,7 @@
         <v>46275</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55627,7 +55627,7 @@
         <v>46276</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>46276</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>46279</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>46234</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45463</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55992,7 +55992,7 @@
         <v>46279</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56065,7 +56065,7 @@
         <v>46276</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56138,7 +56138,7 @@
         <v>45630</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56211,7 +56211,7 @@
         <v>46238</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56284,7 +56284,7 @@
         <v>46280</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>45698</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45726</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>46234</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>46267</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56649,7 +56649,7 @@
         <v>46280</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>46238</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56795,7 +56795,7 @@
         <v>46238</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         <v>46237</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>46238</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>45527</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>45603</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57160,7 +57160,7 @@
         <v>45715</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57233,7 +57233,7 @@
         <v>44992</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57306,7 +57306,7 @@
         <v>45574</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>45401</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45635</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57525,7 +57525,7 @@
         <v>45804</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57598,7 +57598,7 @@
         <v>45804</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45805</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>45818</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57827,7 +57827,7 @@
         <v>45818</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>45820</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>45825</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>45827</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45832</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58197,7 +58197,7 @@
         <v>45833</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>45832</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58343,7 +58343,7 @@
         <v>45709</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58416,7 +58416,7 @@
         <v>45835</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58489,7 +58489,7 @@
         <v>45837</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58562,7 +58562,7 @@
         <v>45840</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58635,7 +58635,7 @@
         <v>45832</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58708,7 +58708,7 @@
         <v>45811</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45820</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58854,7 +58854,7 @@
         <v>45847</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58927,7 +58927,7 @@
         <v>45853</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>45755</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59073,7 +59073,7 @@
         <v>45867</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45769</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>45867</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45869</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45870</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>45870</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>45880</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         <v>45880</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>44237</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59735,7 +59735,7 @@
         <v>44981</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>45351</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59886,7 +59886,7 @@
         <v>44992</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59959,7 +59959,7 @@
         <v>45224</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60032,7 +60032,7 @@
         <v>44587</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60105,7 +60105,7 @@
         <v>45415</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60178,7 +60178,7 @@
         <v>44603</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60251,7 +60251,7 @@
         <v>45378</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60329,7 +60329,7 @@
         <v>45488</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60402,7 +60402,7 @@
         <v>44474</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60475,7 +60475,7 @@
         <v>45488</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>45114</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45488</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60694,7 +60694,7 @@
         <v>45484</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60767,7 +60767,7 @@
         <v>45484</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60840,7 +60840,7 @@
         <v>44610</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60913,7 +60913,7 @@
         <v>44853</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60986,7 +60986,7 @@
         <v>44602</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>45761</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61137,7 +61137,7 @@
         <v>45832</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>45840</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61283,7 +61283,7 @@
         <v>45840</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61356,7 +61356,7 @@
         <v>45840</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61429,7 +61429,7 @@
         <v>45845</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61502,7 +61502,7 @@
         <v>45848</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61575,7 +61575,7 @@
         <v>45884</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61653,7 +61653,7 @@
         <v>45978</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>46065</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61799,7 +61799,7 @@
         <v>46154</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61872,7 +61872,7 @@
         <v>46154</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61945,7 +61945,7 @@
         <v>46169</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62018,7 +62018,7 @@
         <v>46198</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62096,7 +62096,7 @@
         <v>46153</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45121</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>45301</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45755</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45377</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45173</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45678</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45006</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45742</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45077</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45378</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>46145</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>45908</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45072</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45168</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45168</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45786</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45048</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45008</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45674</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45484</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45761</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44670</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45649</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45818</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45667</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44991</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45415</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45399</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45125</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>45104</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46202</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46215</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>46274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>46238</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44600</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45224</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45002</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>45071</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>46073</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44490</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44481</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44670</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44480</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>44824</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44785</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>44578</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44516</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>44826</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44862</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>44588</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>44494</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44483</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44542</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44512</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>44790</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44588</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44588</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>44790</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44790</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>44475</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44670</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44729</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44774</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>44733</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>44733</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44480</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44789</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44508</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44634</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44769</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44612</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44517</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>44819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44480</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44525</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44662</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44564</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44636</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44817</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44676</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44604</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44476</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44854</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44823</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44790</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44620</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>44854</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44722</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44824</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>44742</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44851</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44644</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>44609</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44470</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44776</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44466</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>44866</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44634</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44608</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45090</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44466</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44833</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45215</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44789</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45377</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45100</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45211</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45425</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45090</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45245</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45450</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45308</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45299</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44852</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45539</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45384</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45114</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45266</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45317</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45309</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45257</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45359</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44488</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45359</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44467</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45482</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45371</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45371</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44861</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45533</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45533</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45533</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45147</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45147</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46018</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45884</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45526</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45243</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46028</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>46028</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>46030</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44949</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45171</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45030</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>46030</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44510</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>44984</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44598</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44938</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45483</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44879</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46034</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>46034</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>46035</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45603</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45482</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45618</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45467</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45086</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>46037</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45891</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45527</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46037</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>46037</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>45891</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44918</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45632</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45378</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45498</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44893</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45574</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45715</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45275</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45540</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>46044</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>46043</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46043</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45901</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45901</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44630</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44992</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>44893</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45699</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44994</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45574</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45559</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44587</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44935</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>44603</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>44999</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>44999</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45635</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45517</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>44638</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>46057</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45401</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45915</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45666</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45001</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44587</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45804</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45804</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>44918</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44959</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>46065</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44966</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45495</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44600</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45026</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44910</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45567</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45554</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45567</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45930</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>46083</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45145</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>46083</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45805</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44475</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45202</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45934</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>44943</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44944</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>46091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45394</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46092</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46092</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>46092</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44867</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45581</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>45533</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45588</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>46097</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>46099</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44784</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45176</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45569</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>45947</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>44999</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>46105</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44746</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>46101</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45622</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>45562</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45952</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45075</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45954</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44784</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>46111</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>46112</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>46112</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45343</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>46112</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>46113</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>46113</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>46113</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>46112</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>46112</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>46112</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46112</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>46113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>46112</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>45121</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45959</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45959</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45617</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45959</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45961</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>46121</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44981</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46125</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>44994</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44958</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44965</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45334</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45971</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>44973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45818</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>44977</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46128</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45610</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>44894</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45020</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45114</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45881</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45041</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>46136</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45632</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44745</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45985</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45919</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45224</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45804</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45615</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45867</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45867</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45834</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45632</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>46136</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45749</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45635</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45568</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45033</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45825</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45485</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45924</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45699</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45154</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45923</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45994</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45630</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>44910</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45658</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45189</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>44964</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45063</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44769</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44832</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44546</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45646</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45805</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45818</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44988</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>46002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>46002</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45121</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44502</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>45954</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45820</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45732</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45090</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45090</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45875</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45875</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45768</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45201</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44991</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45113</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45238</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45791</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45063</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45219</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45825</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45754</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45114</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45827</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45482</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>45482</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>45533</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45732</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45111</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>44910</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44598</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44931</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45027</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45112</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45029</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45346</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>44966</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45832</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45832</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>46150</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>44903</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44578</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45709</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>44867</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44879</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45833</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>44903</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44896</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44890</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45835</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>44588</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>46097</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44588</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45837</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>46104</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45981</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45867</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45755</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45361</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45224</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44754</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45100</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45961</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>44517</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45840</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>45110</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45832</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45196</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44607</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>44949</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>45121</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45569</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45820</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45811</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45391</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45086</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45086</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45086</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45847</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>44720</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45853</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44539</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45755</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44553</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>44964</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>44867</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45096</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45111</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45588</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44967</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45769</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45581</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>46175</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45481</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46174</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45867</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45539</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45539</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46176</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45867</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45869</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>46176</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45000</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45552</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>45098</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45870</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45870</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>46181</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45113</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44788</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45581</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>45548</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45020</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>46183</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45569</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45415</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>46184</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45009</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>46184</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45111</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45111</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>45621</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45114</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>46186</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45460</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45533</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45741</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45552</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45271</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45985</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>45880</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46196</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46197</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44585</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>46197</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45572</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45001</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45880</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45182</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>46196</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45377</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>46198</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>46202</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>44579</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>44643</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45328</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45713</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>46203</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>46203</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45071</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46204</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>44795</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45168</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>46206</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>45052</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>46208</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>46206</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45623</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44635</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45330</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>46253</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>46253</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>46253</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45211</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45211</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45650</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>45195</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45351</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>46254</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46213</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45208</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>46256</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45148</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>46213</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45148</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>46256</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45163</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>46256</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45079</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>46213</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45254</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45113</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45897</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>46259</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>44825</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45128</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45196</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>46216</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>46216</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>46216</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45236</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>44663</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45187</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45187</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45707</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46219</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46219</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45308</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45699</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>45174</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>45722</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45761</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45299</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45700</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45623</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>44790</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>45260</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>44820</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>44693</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45245</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45280</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>44956</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>45317</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45219</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>45225</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>45237</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45237</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44732</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>46271</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>46272</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44790</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45323</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>45533</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45355</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45361</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>46231</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45330</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44839</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45217</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46272</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>46272</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>46230</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>46274</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>44578</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>46272</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>46272</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>44897</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>46274</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47753,7 +47753,7 @@
         <v>45091</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45259</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45259</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>46276</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>46233</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>46232</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>46234</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45349</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>46275</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>46276</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>46275</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>46275</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>44599</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>46276</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>46275</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45201</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45674</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45588</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45275</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46280</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>46267</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>46280</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>44495</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>46237</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>46279</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44848</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45440</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>46279</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>44790</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>44861</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>44879</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>46238</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50099,7 +50099,7 @@
         <v>46238</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>45147</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>44987</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>46238</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50391,7 +50391,7 @@
         <v>46238</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50464,7 +50464,7 @@
         <v>46234</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45128</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45481</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>44900</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>46286</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>45394</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>46197</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>44857</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>44585</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>44992</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>44542</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>44566</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51345,7 +51345,7 @@
         <v>46286</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45743</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>45261</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>45048</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>46287</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>46288</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45503</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>44596</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>44952</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52080,7 +52080,7 @@
         <v>46288</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52158,7 +52158,7 @@
         <v>46288</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45215</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>46244</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>46287</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52455,7 +52455,7 @@
         <v>46287</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>46287</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>44992</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>46288</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>46287</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>46210</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52898,7 +52898,7 @@
         <v>44967</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45187</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53044,7 +53044,7 @@
         <v>46176</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45009</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45111</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53263,7 +53263,7 @@
         <v>44909</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>45637</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53409,7 +53409,7 @@
         <v>46175</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45041</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>44961</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>44916</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45300</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45245</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53847,7 +53847,7 @@
         <v>44999</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53920,7 +53920,7 @@
         <v>45495</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53993,7 +53993,7 @@
         <v>45128</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>45128</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>45320</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>44613</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>44992</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45028</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45453</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>45211</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54582,7 +54582,7 @@
         <v>44540</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45174</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54728,7 +54728,7 @@
         <v>44981</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>45138</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>44895</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>45700</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>45163</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45453</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>44963</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>44944</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55312,7 +55312,7 @@
         <v>44944</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45250</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55458,7 +55458,7 @@
         <v>44803</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55531,7 +55531,7 @@
         <v>45153</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45106</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         <v>45106</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55750,7 +55750,7 @@
         <v>45699</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55823,7 +55823,7 @@
         <v>45630</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55896,7 +55896,7 @@
         <v>45224</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         <v>45224</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45558</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>44984</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>45624</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>44984</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>44984</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56412,7 +56412,7 @@
         <v>45350</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56485,7 +56485,7 @@
         <v>45369</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56558,7 +56558,7 @@
         <v>45554</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56631,7 +56631,7 @@
         <v>45722</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45635</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56777,7 +56777,7 @@
         <v>45545</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>45070</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56923,7 +56923,7 @@
         <v>45215</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45720</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57069,7 +57069,7 @@
         <v>44991</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         <v>44994</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>45149</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>45169</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45278</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>45456</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>45174</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>45533</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45533</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>44965</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>44875</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>45171</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45475</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45061</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58106,7 +58106,7 @@
         <v>44510</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58184,7 +58184,7 @@
         <v>45301</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>45301</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45475</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>45124</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>45759</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45530</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>45128</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>45232</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>45525</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58841,7 +58841,7 @@
         <v>45565</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>45257</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45018</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45607</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59133,7 +59133,7 @@
         <v>45301</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59206,7 +59206,7 @@
         <v>45513</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59279,7 +59279,7 @@
         <v>45513</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59352,7 +59352,7 @@
         <v>45110</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59425,7 +59425,7 @@
         <v>45415</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59498,7 +59498,7 @@
         <v>45391</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59571,7 +59571,7 @@
         <v>45111</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59644,7 +59644,7 @@
         <v>45481</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59717,7 +59717,7 @@
         <v>45463</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59790,7 +59790,7 @@
         <v>45630</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         <v>45726</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59936,7 +59936,7 @@
         <v>45698</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60009,7 +60009,7 @@
         <v>44237</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60082,7 +60082,7 @@
         <v>44587</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60155,7 +60155,7 @@
         <v>44603</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60228,7 +60228,7 @@
         <v>44610</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>44602</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60374,7 +60374,7 @@
         <v>44981</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45351</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60525,7 +60525,7 @@
         <v>44992</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60598,7 +60598,7 @@
         <v>45224</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60671,7 +60671,7 @@
         <v>45415</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60744,7 +60744,7 @@
         <v>45378</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60822,7 +60822,7 @@
         <v>45488</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>44474</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45488</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45114</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         <v>45488</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61187,7 +61187,7 @@
         <v>45484</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61260,7 +61260,7 @@
         <v>45484</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61333,7 +61333,7 @@
         <v>44853</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61406,7 +61406,7 @@
         <v>45761</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>45832</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61557,7 +61557,7 @@
         <v>45840</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45840</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
         <v>45840</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45845</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45848</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61922,7 +61922,7 @@
         <v>45884</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62000,7 +62000,7 @@
         <v>45978</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>46065</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62146,7 +62146,7 @@
         <v>46154</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>46154</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>46169</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62365,7 +62365,7 @@
         <v>46198</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62443,7 +62443,7 @@
         <v>46153</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45121</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>45301</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45755</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45377</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45173</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45678</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45006</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45742</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45926</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45077</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45378</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>46145</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>45908</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45072</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45760</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>45168</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>45168</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>45786</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45048</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45008</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
         <v>46205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
         <v>45674</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45484</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45761</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44670</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45649</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>45959</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>45818</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45667</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44991</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45415</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45399</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45125</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>45104</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>46202</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>46215</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>46274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>46238</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44600</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45224</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45002</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44803</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>45071</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>45848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>46073</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44490</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44481</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>44614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>44670</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44480</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         <v>44824</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
         <v>44785</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>44578</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44516</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>44826</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44862</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>44603</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>44588</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>44494</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44483</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44542</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>44512</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>44790</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44588</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44588</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>44790</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44790</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>44475</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44670</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>44729</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44774</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>44733</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>44733</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44480</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>44789</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44508</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>44634</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44769</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>44612</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>44517</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>44819</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>44480</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44525</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>44662</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44564</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44636</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>44817</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         <v>44676</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11209,7 +11209,7 @@
         <v>44604</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44476</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44854</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44823</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44790</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44620</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>44854</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44722</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>44824</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>44742</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>44851</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44644</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>44621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>44876</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12231,7 +12231,7 @@
         <v>44733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>44609</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>44470</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44776</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44466</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>44866</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44634</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44608</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>45090</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44466</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>45105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44833</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>45215</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44789</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45377</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45100</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45211</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45425</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45090</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45245</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45450</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45308</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45299</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>44852</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45539</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>45384</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>45114</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45266</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45317</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45309</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>45257</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>45359</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44488</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>45359</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44467</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>45482</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45371</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>45371</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44861</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45533</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>45533</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15609,7 +15609,7 @@
         <v>45533</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>45147</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>45147</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46018</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45884</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45526</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45243</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46028</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>46028</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>46030</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44949</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45171</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45030</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>46030</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16646,7 +16646,7 @@
         <v>44510</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>44984</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>44598</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>44938</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45483</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>44879</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46034</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>46034</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>46035</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45603</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>45482</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>45618</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45467</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45086</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>46037</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45891</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45527</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46037</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>46037</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>45891</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45891</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>44918</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45632</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45378</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45498</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44893</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45574</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45715</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45275</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45540</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>46044</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>46043</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46043</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45901</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45901</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44630</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>44992</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>44893</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45699</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44994</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45574</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45559</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>44587</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44935</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>44603</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>44999</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>44999</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45635</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>44964</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45517</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>44638</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>46057</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45401</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45915</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45666</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45001</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>44587</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45804</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45804</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>44918</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>44959</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>46065</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>44966</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45495</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44600</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45026</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>44910</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45567</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45554</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45567</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45930</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>46083</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45145</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>46083</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>45805</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>44475</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45202</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45934</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>44943</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>44944</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>46091</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45394</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>46092</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22861,7 +22861,7 @@
         <v>46092</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22934,7 +22934,7 @@
         <v>46092</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44867</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45581</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>45533</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>45588</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>46097</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>46099</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>44784</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>45176</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23596,7 +23596,7 @@
         <v>45569</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         <v>45947</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>44999</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>46105</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44746</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>46101</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45622</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>45562</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45952</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45075</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45954</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>44784</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>46111</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>46112</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>46112</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45343</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>46112</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>46113</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>46113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>46113</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>46113</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>46112</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>46112</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>46112</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>46112</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>46113</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>46112</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         <v>45121</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45959</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45959</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45617</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45959</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45961</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>46121</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44981</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46125</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>44994</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>44958</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44965</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45334</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45971</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>44973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45818</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>44977</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46128</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45610</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>44894</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44992</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45020</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>45114</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45881</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45041</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>46136</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45632</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>44745</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45985</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45919</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>45224</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45804</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45615</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45867</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45867</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45834</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45632</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>46136</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45749</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45635</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45568</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45033</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45825</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45485</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45924</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45699</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45154</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45923</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45994</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45630</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>44910</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45658</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45189</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>44964</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45063</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>44769</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>44832</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>44546</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45646</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45805</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45818</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>44988</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>46002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>46002</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45121</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44502</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30533,7 +30533,7 @@
         <v>45954</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30606,7 +30606,7 @@
         <v>45820</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>45992</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45732</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45090</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30898,7 +30898,7 @@
         <v>45090</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>45875</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45875</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45768</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45201</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44991</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45113</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>45238</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45791</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45063</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>45219</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31701,7 +31701,7 @@
         <v>45825</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45754</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45114</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45827</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31993,7 +31993,7 @@
         <v>45482</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32066,7 +32066,7 @@
         <v>45482</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>45533</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>45732</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45111</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32358,7 +32358,7 @@
         <v>44910</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>44598</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32504,7 +32504,7 @@
         <v>44931</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45027</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45112</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45029</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45346</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>44966</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45832</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45832</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>46150</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>44903</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44578</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45709</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>44867</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44879</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45833</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>44903</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44896</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44890</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>45835</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>44588</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>46097</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>44588</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45837</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>46104</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45981</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45867</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45755</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45361</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>45224</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34636,7 +34636,7 @@
         <v>44754</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45100</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45961</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>44517</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>45840</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>45110</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45832</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45196</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>44607</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>44949</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35371,7 +35371,7 @@
         <v>45121</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35449,7 +35449,7 @@
         <v>45569</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45820</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45811</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35668,7 +35668,7 @@
         <v>45391</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>45086</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35814,7 +35814,7 @@
         <v>45086</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35887,7 +35887,7 @@
         <v>45086</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45847</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>44720</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36106,7 +36106,7 @@
         <v>45853</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>44539</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45755</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44553</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>44964</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>44867</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45096</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45111</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45588</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>44967</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45769</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45581</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>46175</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45481</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>46174</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45867</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45539</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45539</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46176</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45867</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>45869</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>46176</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45000</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45552</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>45098</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45870</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45870</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>46181</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45113</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38223,7 +38223,7 @@
         <v>44788</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45581</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>45548</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45020</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>46183</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45569</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45415</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38734,7 +38734,7 @@
         <v>46184</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>45009</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>46184</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38953,7 +38953,7 @@
         <v>45111</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39026,7 +39026,7 @@
         <v>45111</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39099,7 +39099,7 @@
         <v>45621</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45114</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>46186</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>45460</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45533</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45741</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45552</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45271</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45985</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>45880</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>46196</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>46197</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44585</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>46197</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45572</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45001</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45880</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45182</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>46196</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45377</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>46198</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40647,7 +40647,7 @@
         <v>46202</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         <v>44579</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>44643</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45328</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40939,7 +40939,7 @@
         <v>45713</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>46203</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>46203</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45071</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46204</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41309,7 +41309,7 @@
         <v>44795</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45168</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>46206</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>45052</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>46208</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>46206</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45623</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44635</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45330</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>46253</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>46253</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>46253</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45211</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>45211</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>45650</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>45195</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45351</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>46254</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46213</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45208</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>46256</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45148</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>46213</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45148</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>46256</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>45163</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>46256</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45079</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>46213</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45254</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45113</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45897</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>46259</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>44825</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45128</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>45196</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>46216</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>46216</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>46216</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44161,7 +44161,7 @@
         <v>45236</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44234,7 +44234,7 @@
         <v>44663</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45187</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45187</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44453,7 +44453,7 @@
         <v>45707</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44526,7 +44526,7 @@
         <v>46219</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44599,7 +44599,7 @@
         <v>46219</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45308</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45699</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44818,7 +44818,7 @@
         <v>45174</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>45722</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>45761</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45037,7 +45037,7 @@
         <v>45299</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45700</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45623</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>44790</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>45260</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>44820</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>44693</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45553,7 +45553,7 @@
         <v>45245</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45280</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>44956</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>45317</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45219</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45928,7 +45928,7 @@
         <v>45225</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46001,7 +46001,7 @@
         <v>45237</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46074,7 +46074,7 @@
         <v>45237</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46147,7 +46147,7 @@
         <v>44732</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46220,7 +46220,7 @@
         <v>46271</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>46272</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>44790</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46439,7 +46439,7 @@
         <v>45323</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>45533</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45355</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45361</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>46231</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46804,7 +46804,7 @@
         <v>45330</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44839</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45217</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46272</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>46272</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>46230</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>46274</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>44578</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47388,7 +47388,7 @@
         <v>46272</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>46272</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47607,7 +47607,7 @@
         <v>44897</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47680,7 +47680,7 @@
         <v>46274</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47753,7 +47753,7 @@
         <v>45091</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45259</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45259</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>46276</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>46233</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>46232</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48201,7 +48201,7 @@
         <v>46234</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45349</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>46275</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>46276</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>46275</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>46275</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>44599</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>46276</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>46275</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>45201</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45674</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45588</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45275</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>46280</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>46267</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>46280</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>44495</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>46237</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>46279</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>44848</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45440</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>46279</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>44790</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>44861</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>44879</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>46238</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50099,7 +50099,7 @@
         <v>46238</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         <v>45147</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>44987</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50318,7 +50318,7 @@
         <v>46238</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50391,7 +50391,7 @@
         <v>46238</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50464,7 +50464,7 @@
         <v>46234</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>45128</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45481</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>44900</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>46286</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>45394</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50902,7 +50902,7 @@
         <v>46197</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50975,7 +50975,7 @@
         <v>44857</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>44585</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51121,7 +51121,7 @@
         <v>44992</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>44542</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51272,7 +51272,7 @@
         <v>44566</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51345,7 +51345,7 @@
         <v>46286</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45743</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>45261</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>45048</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>46287</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>46288</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51788,7 +51788,7 @@
         <v>45503</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>44596</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>44952</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52080,7 +52080,7 @@
         <v>46288</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52158,7 +52158,7 @@
         <v>46288</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>45215</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52309,7 +52309,7 @@
         <v>46244</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>46287</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52455,7 +52455,7 @@
         <v>46287</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>46287</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>44992</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>46288</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>46287</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>46210</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52898,7 +52898,7 @@
         <v>44967</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45187</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53044,7 +53044,7 @@
         <v>46176</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>45009</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45111</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53263,7 +53263,7 @@
         <v>44909</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>45637</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53409,7 +53409,7 @@
         <v>46175</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45041</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>44961</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>44916</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>45300</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45245</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53847,7 +53847,7 @@
         <v>44999</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53920,7 +53920,7 @@
         <v>45495</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53993,7 +53993,7 @@
         <v>45128</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>45128</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>45320</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>44613</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>44992</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>45028</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45453</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>45211</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54582,7 +54582,7 @@
         <v>44540</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54655,7 +54655,7 @@
         <v>45174</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54728,7 +54728,7 @@
         <v>44981</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54801,7 +54801,7 @@
         <v>45138</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54874,7 +54874,7 @@
         <v>44895</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>45700</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>45163</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55093,7 +55093,7 @@
         <v>45453</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>44963</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>44944</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55312,7 +55312,7 @@
         <v>44944</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>45250</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55458,7 +55458,7 @@
         <v>44803</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55531,7 +55531,7 @@
         <v>45153</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55604,7 +55604,7 @@
         <v>45106</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55677,7 +55677,7 @@
         <v>45106</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55750,7 +55750,7 @@
         <v>45699</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55823,7 +55823,7 @@
         <v>45630</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55896,7 +55896,7 @@
         <v>45224</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         <v>45224</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>45558</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56120,7 +56120,7 @@
         <v>44984</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56193,7 +56193,7 @@
         <v>45624</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56266,7 +56266,7 @@
         <v>44984</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>44984</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56412,7 +56412,7 @@
         <v>45350</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56485,7 +56485,7 @@
         <v>45369</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56558,7 +56558,7 @@
         <v>45554</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56631,7 +56631,7 @@
         <v>45722</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56704,7 +56704,7 @@
         <v>45635</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56777,7 +56777,7 @@
         <v>45545</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>45070</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56923,7 +56923,7 @@
         <v>45215</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45720</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57069,7 +57069,7 @@
         <v>44991</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         <v>44994</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57215,7 +57215,7 @@
         <v>45149</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>45169</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57361,7 +57361,7 @@
         <v>45278</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>45456</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57512,7 +57512,7 @@
         <v>45174</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>45533</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>45533</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>44965</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>44875</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>45171</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45475</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>45061</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58106,7 +58106,7 @@
         <v>44510</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58184,7 +58184,7 @@
         <v>45301</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58257,7 +58257,7 @@
         <v>45301</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58330,7 +58330,7 @@
         <v>45475</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58403,7 +58403,7 @@
         <v>45124</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58476,7 +58476,7 @@
         <v>45759</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45530</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58622,7 +58622,7 @@
         <v>45128</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58695,7 +58695,7 @@
         <v>45232</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58768,7 +58768,7 @@
         <v>45525</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58841,7 +58841,7 @@
         <v>45565</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58914,7 +58914,7 @@
         <v>45257</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58987,7 +58987,7 @@
         <v>45018</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59060,7 +59060,7 @@
         <v>45607</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59133,7 +59133,7 @@
         <v>45301</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59206,7 +59206,7 @@
         <v>45513</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59279,7 +59279,7 @@
         <v>45513</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59352,7 +59352,7 @@
         <v>45110</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59425,7 +59425,7 @@
         <v>45415</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59498,7 +59498,7 @@
         <v>45391</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59571,7 +59571,7 @@
         <v>45111</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59644,7 +59644,7 @@
         <v>45481</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59717,7 +59717,7 @@
         <v>45463</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59790,7 +59790,7 @@
         <v>45630</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59863,7 +59863,7 @@
         <v>45726</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59936,7 +59936,7 @@
         <v>45698</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60009,7 +60009,7 @@
         <v>44237</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60082,7 +60082,7 @@
         <v>44587</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60155,7 +60155,7 @@
         <v>44603</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60228,7 +60228,7 @@
         <v>44610</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>44602</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60374,7 +60374,7 @@
         <v>44981</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45351</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60525,7 +60525,7 @@
         <v>44992</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60598,7 +60598,7 @@
         <v>45224</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60671,7 +60671,7 @@
         <v>45415</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60744,7 +60744,7 @@
         <v>45378</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60822,7 +60822,7 @@
         <v>45488</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>44474</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45488</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>45114</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         <v>45488</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61187,7 +61187,7 @@
         <v>45484</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61260,7 +61260,7 @@
         <v>45484</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61333,7 +61333,7 @@
         <v>44853</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61406,7 +61406,7 @@
         <v>45761</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>45832</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61557,7 +61557,7 @@
         <v>45840</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45840</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
         <v>45840</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45845</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61849,7 +61849,7 @@
         <v>45848</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61922,7 +61922,7 @@
         <v>45884</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62000,7 +62000,7 @@
         <v>45978</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>46065</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62146,7 +62146,7 @@
         <v>46154</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>46154</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>46169</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62365,7 +62365,7 @@
         <v>46198</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62443,7 +62443,7 @@
         <v>46153</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45377</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45173</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45678</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45006</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45077</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45742</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45926</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45378</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>46145</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45908</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45072</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45168</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>45168</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>45786</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46205</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45008</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45760</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>45048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45484</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45761</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44670</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44991</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>45104</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45224</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45959</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45649</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45667</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45818</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>45399</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45415</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>46202</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44600</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>46274</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>46238</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>46293</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>46215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>46296</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>45574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>44803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45848</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>46073</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44490</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44481</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44670</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44509</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44480</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44785</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44826</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>44578</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44862</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44603</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44483</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44542</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44494</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44512</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44790</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44530</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44588</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44588</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44790</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44790</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>44475</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44670</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44729</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44774</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44733</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44480</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>44588</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>44634</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44480</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44769</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44612</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44819</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>44608</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44480</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44564</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44636</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44817</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44676</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44604</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44476</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44854</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44823</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44854</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44790</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>44620</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44722</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44824</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>44742</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44851</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44644</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44621</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44876</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44776</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44866</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44608</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44588</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44588</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44634</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45111</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45114</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45624</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45617</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45411</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45033</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>44607</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>44903</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44991</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44991</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45196</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44879</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44981</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45261</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>44910</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44693</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45346</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45732</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45147</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45610</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45453</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>44992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45020</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45052</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>44992</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45394</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45299</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45623</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45552</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45607</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45674</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45630</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45698</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>46002</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>45224</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>46002</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>45726</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44720</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45539</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45884</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44966</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45482</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45237</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>45533</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45097</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44931</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>45328</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>46018</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45558</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45309</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45891</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45891</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44861</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>45891</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>45300</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>45254</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45350</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>46028</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>46028</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45063</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>46030</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45901</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>46030</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>46034</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46034</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46035</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45145</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>46037</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45187</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46037</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46037</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>44981</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45163</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46043</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44510</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44553</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46043</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46044</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45217</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44566</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>44488</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44918</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45450</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45527</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45163</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44988</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45603</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45715</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44992</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45275</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45168</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45574</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45187</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45401</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44754</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45635</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45804</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45552</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45804</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45805</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44769</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45128</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45171</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45650</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>46057</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44613</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45128</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45189</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45540</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45930</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45425</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45475</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>46065</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45232</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45934</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45482</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>44867</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45236</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45121</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44967</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44903</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45174</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45317</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>44857</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45359</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45947</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44944</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>44944</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45467</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45000</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45952</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45440</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>46083</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45495</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45554</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>46083</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45257</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45954</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45959</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44999</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45301</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44789</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45961</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>46091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>46092</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46092</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46092</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44958</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45219</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44663</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45567</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45623</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45041</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46097</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45201</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45971</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45086</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>46099</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44599</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44944</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>46101</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45330</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45250</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>45225</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45818</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>45818</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>46105</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45700</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44539</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45299</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>44910</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44598</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>46111</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>46112</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>46112</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>44848</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>46112</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>46112</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46112</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46112</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45559</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>46112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>46112</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45224</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46113</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45820</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45415</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46113</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>46113</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44542</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>46113</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45825</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>44984</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45245</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45732</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>46121</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45707</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45994</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>46125</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>46128</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>44578</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45827</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45525</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>44964</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45121</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45211</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45075</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>44630</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45832</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45371</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>45833</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45100</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44910</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44795</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45832</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45804</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45280</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45112</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45709</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45111</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45835</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45202</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45992</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45632</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45245</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44585</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45170</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>45224</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45867</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45867</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45485</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45837</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45840</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45832</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44867</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44732</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45635</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45811</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45483</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45820</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45954</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45713</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45615</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45881</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45658</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45847</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>46136</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44984</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44984</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45018</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45825</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45105</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44788</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45853</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45070</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45028</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45456</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45755</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45481</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44964</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45257</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45749</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45875</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45875</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45533</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45533</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45001</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45569</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46136</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44879</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45475</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44510</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>44961</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>44984</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45923</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45090</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45924</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45919</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45805</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45834</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45174</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45632</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45091</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44964</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44832</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45646</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45867</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>45769</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45545</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45361</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>45791</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45867</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>44896</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>45699</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45114</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45869</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45111</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45111</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45098</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45768</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45154</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45722</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45481</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>45453</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44502</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>45378</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45377</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45219</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45870</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45211</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44977</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45498</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45870</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44825</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>45215</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45533</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45754</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45187</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44475</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>44839</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>46150</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44875</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45533</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>44973</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45106</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45301</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>45722</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>45106</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45743</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45569</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45148</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45361</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44952</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45548</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>46104</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45867</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>45394</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45138</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45755</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45981</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45317</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45384</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45961</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45513</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45513</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45637</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45153</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>45880</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39752,7 +39752,7 @@
         <v>45635</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45211</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44890</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45278</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45029</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45588</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45699</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45880</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45086</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45128</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>44635</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46174</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46175</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>45343</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>46176</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45581</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45539</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>46176</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45301</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44546</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45369</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45526</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>46181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45741</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>46183</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>46184</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45622</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45574</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>45533</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41889,7 +41889,7 @@
         <v>46186</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44833</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>45985</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>44897</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>45498</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45009</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>46196</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44992</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>46196</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>46197</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>46198</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>44999</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44999</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45148</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>46197</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45581</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45495</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45618</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45699</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>46203</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45259</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45259</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45562</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45086</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>44517</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45533</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45121</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
         <v>45275</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43953,7 +43953,7 @@
         <v>46203</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>44746</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>44598</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>46208</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45330</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45079</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>46206</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>44579</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>44495</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45090</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>45090</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>44638</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>46216</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46259</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>46216</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>46216</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>46213</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45267,7 +45267,7 @@
         <v>46256</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45245</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45897</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45415</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>46213</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45621</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>46256</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>46256</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         <v>44861</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>45308</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>46213</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45063</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>44895</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45009</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>46219</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>44820</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>45215</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45215</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46581,7 +46581,7 @@
         <v>46219</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45351</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45539</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45565</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45482</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45026</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45266</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45554</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>45632</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47311,7 +47311,7 @@
         <v>44803</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45567</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>46271</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>44587</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45110</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>46230</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>46231</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>46272</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45503</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>46272</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46272</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>46272</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>44956</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46272</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>46275</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>46275</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>46274</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>46232</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>46275</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>46274</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>46233</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>46275</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>46276</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>46276</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>46279</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46234</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>44596</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>46279</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>46276</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45113</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45666</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>46238</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>46234</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>46267</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>44918</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>46280</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45027</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50168,7 +50168,7 @@
         <v>46238</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>46238</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45224</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>46237</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50465,7 +50465,7 @@
         <v>46238</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45377</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         <v>45114</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45349</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>45334</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45114</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>44600</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45581</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45359</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>44895</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>44587</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>46286</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45569</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>45588</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45355</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>44949</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>46286</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>46197</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>46210</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45090</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>44790</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>46244</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>46287</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>44784</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>44935</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>44852</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52363,7 +52363,7 @@
         <v>45100</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>46288</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>45517</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>44578</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>44994</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>44900</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45201</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44966</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46288</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>46287</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>46287</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>46287</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46287</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>46288</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53400,7 +53400,7 @@
         <v>45323</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>46287</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>46288</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         <v>45308</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45111</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45086</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45196</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45320</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>44987</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>45208</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>45001</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         <v>45901</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>44585</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>45260</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>44992</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>44943</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>45371</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>46176</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>46175</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>44938</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54875,7 +54875,7 @@
         <v>44949</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>45020</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45568</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>46294</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>44894</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>44790</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>44790</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>46254</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45211</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>44893</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45174</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>46253</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>46253</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>46297</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>46296</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>44994</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45176</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45759</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45061</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56272,7 +56272,7 @@
         <v>46296</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45096</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         <v>46253</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56491,7 +56491,7 @@
         <v>46296</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56564,7 +56564,7 @@
         <v>46296</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>46204</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>46202</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>45391</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45630</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45110</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45182</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57080,7 +57080,7 @@
         <v>45761</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         <v>45128</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57226,7 +57226,7 @@
         <v>45128</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57299,7 +57299,7 @@
         <v>44999</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         <v>45530</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45483</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>45271</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>45113</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>44540</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>44916</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>45149</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>45482</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>44879</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58029,7 +58029,7 @@
         <v>45700</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>44603</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45147</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>44959</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58321,7 +58321,7 @@
         <v>45171</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>45113</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>44967</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>44963</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45720</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>44909</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45699</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>44784</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58905,7 +58905,7 @@
         <v>45243</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>44643</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>45238</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59124,7 +59124,7 @@
         <v>44893</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45572</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45147</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45169</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59416,7 +59416,7 @@
         <v>44867</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>44745</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45630</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>45533</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>45533</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45124</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59859,7 +59859,7 @@
         <v>45071</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59932,7 +59932,7 @@
         <v>45481</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45111</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60078,7 +60078,7 @@
         <v>45391</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>45463</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>44237</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60297,7 +60297,7 @@
         <v>44981</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60375,7 +60375,7 @@
         <v>45351</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60448,7 +60448,7 @@
         <v>44992</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60521,7 +60521,7 @@
         <v>45224</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60594,7 +60594,7 @@
         <v>44587</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45415</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>44603</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60813,7 +60813,7 @@
         <v>45378</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60891,7 +60891,7 @@
         <v>45488</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>44474</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45488</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61110,7 +61110,7 @@
         <v>45114</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>45488</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61256,7 +61256,7 @@
         <v>45484</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61329,7 +61329,7 @@
         <v>45484</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61402,7 +61402,7 @@
         <v>44610</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>44853</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61548,7 +61548,7 @@
         <v>44602</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45761</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61699,7 +61699,7 @@
         <v>45832</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61772,7 +61772,7 @@
         <v>45840</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45840</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>45840</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45845</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>45848</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>45884</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45978</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>46065</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62361,7 +62361,7 @@
         <v>46154</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62434,7 +62434,7 @@
         <v>46154</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62507,7 +62507,7 @@
         <v>46169</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62580,7 +62580,7 @@
         <v>46198</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62658,7 +62658,7 @@
         <v>46153</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>46293</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>46293</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>45121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>45377</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45173</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45678</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>45006</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>46100</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45979</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45077</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>45742</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45926</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>45020</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45378</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>46145</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44943</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>45908</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45072</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45168</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>45168</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>45786</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46205</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>45008</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>45760</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>45048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45378</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45484</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>45761</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>44670</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>44991</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>45104</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45224</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44595</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45959</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45649</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>45070</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45667</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         <v>45818</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         <v>45125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>45399</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>45415</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>46202</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44600</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>46274</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>46238</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>46293</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>46215</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>46296</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>45574</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>44803</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45848</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>46073</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44490</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>44481</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>44614</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>44670</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44509</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44480</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>44824</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>44785</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44826</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>44578</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44862</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44603</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44588</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44483</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44542</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44494</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44512</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44790</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44530</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44588</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44588</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44790</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44790</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>44475</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44670</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44729</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44774</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44733</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44733</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44480</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>44588</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44508</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         <v>44634</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44480</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44769</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44612</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44819</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>44608</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44480</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>44564</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>44636</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11278,7 +11278,7 @@
         <v>44817</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44676</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11424,7 +11424,7 @@
         <v>44604</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44476</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44854</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>44823</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44854</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44790</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>44620</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44722</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44824</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>44742</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44851</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44644</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44621</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44876</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44733</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44776</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44866</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44608</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44817</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44588</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44588</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44634</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45111</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45114</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45624</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45617</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45411</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45033</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>44607</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>44903</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44994</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44991</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44991</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45196</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>45048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>44879</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44981</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45261</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>44910</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>44693</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>45346</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45732</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>45147</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>45610</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>45453</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
         <v>44992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>45020</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45052</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15011,7 +15011,7 @@
         <v>44992</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15084,7 +15084,7 @@
         <v>45588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>45394</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>45299</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45623</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45552</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15449,7 +15449,7 @@
         <v>45607</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>45674</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45630</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15668,7 +15668,7 @@
         <v>45698</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>46002</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45030</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>45224</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15970,7 +15970,7 @@
         <v>46002</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>45726</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44720</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45539</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>45884</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16345,7 +16345,7 @@
         <v>44966</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>45482</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45237</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16637,7 +16637,7 @@
         <v>45533</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45097</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>44931</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>44965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>45328</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17017,7 +17017,7 @@
         <v>46018</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45558</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>45309</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45891</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45891</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44861</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>45891</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>45300</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>45254</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45350</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>46028</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>46028</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45063</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>46030</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45901</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>46030</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>46034</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46034</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>46035</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45145</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>46037</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45187</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46037</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46037</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>44981</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45163</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>46043</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44510</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>44553</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>46043</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>46044</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45915</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45915</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45217</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44566</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>44488</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44918</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45450</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45527</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45163</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44988</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45603</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45715</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44992</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45275</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45168</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45574</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45187</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45401</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>44754</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45635</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45804</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45552</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45804</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>45805</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>44769</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>45128</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21261,7 +21261,7 @@
         <v>45171</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21334,7 +21334,7 @@
         <v>45650</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>46057</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>44613</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45128</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45189</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45540</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45930</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45425</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45475</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>46065</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45232</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45934</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45482</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>44867</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45236</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45121</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44967</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44903</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45174</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45317</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>44857</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45359</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45947</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44944</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>44944</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45467</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45000</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45952</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45440</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>46083</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45495</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45554</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>46083</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45257</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45954</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45959</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45959</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44999</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45959</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45301</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>44789</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>45961</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>46091</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>46092</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>46092</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>46092</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44958</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45219</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44663</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45567</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45623</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45041</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>46097</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45201</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45971</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45086</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>46099</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44599</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>44944</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>46101</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45330</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45250</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>45225</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45818</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26162,7 +26162,7 @@
         <v>45818</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>46105</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45700</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>44539</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45299</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>44910</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>44598</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>46111</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>46112</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>46112</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>44848</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>46112</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>46112</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46112</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>46112</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>45559</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>46112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>46112</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45224</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46113</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>45820</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45415</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46113</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>46113</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>44542</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>46113</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28246,7 +28246,7 @@
         <v>45825</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28319,7 +28319,7 @@
         <v>44984</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>45245</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45732</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>46121</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28611,7 +28611,7 @@
         <v>45707</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         <v>45994</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28757,7 +28757,7 @@
         <v>46125</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28830,7 +28830,7 @@
         <v>46128</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>44578</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45827</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45525</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>44964</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45121</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>45211</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45075</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>44630</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45832</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45371</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>45833</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45100</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>44910</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44795</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45832</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45804</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45280</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30149,7 +30149,7 @@
         <v>45112</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30222,7 +30222,7 @@
         <v>45709</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30295,7 +30295,7 @@
         <v>45111</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30368,7 +30368,7 @@
         <v>45835</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30441,7 +30441,7 @@
         <v>45202</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>45992</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45632</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>45245</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>44585</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>45170</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>45224</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45867</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>45867</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45485</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>45837</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45840</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45832</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44867</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44732</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>45635</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45811</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45483</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31760,7 +31760,7 @@
         <v>45820</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
         <v>45954</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>45713</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45615</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32052,7 +32052,7 @@
         <v>45881</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32125,7 +32125,7 @@
         <v>45658</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32198,7 +32198,7 @@
         <v>45847</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>46136</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44984</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>44984</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45018</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>45825</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45105</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44788</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45853</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45070</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45028</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45456</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45755</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>45481</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>44964</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45257</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45749</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45875</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45875</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45533</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45533</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45001</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45569</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46136</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33965,7 +33965,7 @@
         <v>44879</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45475</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>44510</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>44961</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>44984</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45923</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45090</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45924</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45919</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>45805</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>45834</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45174</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45632</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45091</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>44964</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>44832</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45646</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45867</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>45769</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45545</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45361</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35508,7 +35508,7 @@
         <v>45791</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35581,7 +35581,7 @@
         <v>45867</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
         <v>44896</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>45699</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>45114</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45869</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45111</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45111</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45098</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45768</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36238,7 +36238,7 @@
         <v>45154</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45722</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36384,7 +36384,7 @@
         <v>45481</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>45453</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36530,7 +36530,7 @@
         <v>44502</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36603,7 +36603,7 @@
         <v>45378</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36676,7 +36676,7 @@
         <v>45377</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45219</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>45870</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45211</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44977</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45498</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45870</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>44825</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>45215</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         <v>45533</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37411,7 +37411,7 @@
         <v>45754</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37484,7 +37484,7 @@
         <v>45187</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>44475</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>44839</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>46150</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44875</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45533</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>44973</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37995,7 +37995,7 @@
         <v>45106</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45301</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38141,7 +38141,7 @@
         <v>45722</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>45106</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38287,7 +38287,7 @@
         <v>45743</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45569</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45148</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45361</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44952</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45548</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>46104</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38798,7 +38798,7 @@
         <v>45867</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>45394</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>45138</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45755</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39090,7 +39090,7 @@
         <v>45981</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45317</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45384</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>45961</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45513</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45513</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45637</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45153</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>45880</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39752,7 +39752,7 @@
         <v>45635</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39825,7 +39825,7 @@
         <v>45211</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>44890</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45278</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45029</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40122,7 +40122,7 @@
         <v>45588</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>45699</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45880</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40346,7 +40346,7 @@
         <v>45086</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40419,7 +40419,7 @@
         <v>45128</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>44635</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>46174</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40638,7 +40638,7 @@
         <v>46175</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40711,7 +40711,7 @@
         <v>45343</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>46176</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40857,7 +40857,7 @@
         <v>45581</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40930,7 +40930,7 @@
         <v>45539</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41003,7 +41003,7 @@
         <v>46176</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>45301</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>44546</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45369</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>45526</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>46181</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45741</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>46183</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>46184</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45622</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45574</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41811,7 +41811,7 @@
         <v>45533</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41889,7 +41889,7 @@
         <v>46186</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44833</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>45985</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42108,7 +42108,7 @@
         <v>44897</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42181,7 +42181,7 @@
         <v>45498</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42254,7 +42254,7 @@
         <v>45009</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>46196</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44992</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>46196</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>46197</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>46198</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42697,7 +42697,7 @@
         <v>44999</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44999</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45148</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>46197</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>45581</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45495</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45618</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45699</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>46203</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45259</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45259</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43510,7 +43510,7 @@
         <v>45562</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>45086</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43656,7 +43656,7 @@
         <v>44517</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45533</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45121</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
         <v>45275</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43953,7 +43953,7 @@
         <v>46203</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>44746</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44099,7 +44099,7 @@
         <v>44598</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>46208</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44245,7 +44245,7 @@
         <v>45330</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>45079</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>46206</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>44579</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>46206</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44610,7 +44610,7 @@
         <v>44495</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45090</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>45090</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>44638</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>46216</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46259</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>46216</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>46216</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>46213</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45267,7 +45267,7 @@
         <v>46256</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45245</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45413,7 +45413,7 @@
         <v>45897</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45415</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>46213</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45632,7 +45632,7 @@
         <v>45621</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>46256</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>46256</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         <v>44861</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45924,7 +45924,7 @@
         <v>45308</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>46213</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45063</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46143,7 +46143,7 @@
         <v>44895</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45009</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46289,7 +46289,7 @@
         <v>46219</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46362,7 +46362,7 @@
         <v>44820</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>45215</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>45215</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46581,7 +46581,7 @@
         <v>46219</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45351</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45539</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45565</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>45482</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>45195</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45026</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>45266</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45554</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>45632</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47311,7 +47311,7 @@
         <v>44803</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47384,7 +47384,7 @@
         <v>45567</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>46271</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>44587</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47603,7 +47603,7 @@
         <v>46272</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45110</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>46230</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47822,7 +47822,7 @@
         <v>46231</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>46272</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47968,7 +47968,7 @@
         <v>45503</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>46272</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48114,7 +48114,7 @@
         <v>46272</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>46272</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>44956</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46272</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48411,7 +48411,7 @@
         <v>46275</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>46275</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>46274</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>46232</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>46275</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>46274</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>46233</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48922,7 +48922,7 @@
         <v>46275</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>46276</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>46276</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49141,7 +49141,7 @@
         <v>46279</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49214,7 +49214,7 @@
         <v>46234</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>44596</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49360,7 +49360,7 @@
         <v>46279</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>46276</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45113</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45666</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>46238</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49725,7 +49725,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         <v>46234</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>46267</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>44918</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>46280</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50090,7 +50090,7 @@
         <v>45027</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50168,7 +50168,7 @@
         <v>46238</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>46238</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50314,7 +50314,7 @@
         <v>45224</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50392,7 +50392,7 @@
         <v>46237</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50465,7 +50465,7 @@
         <v>46238</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50538,7 +50538,7 @@
         <v>45377</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50611,7 +50611,7 @@
         <v>45114</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45349</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50757,7 +50757,7 @@
         <v>45334</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>45114</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50903,7 +50903,7 @@
         <v>44600</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45581</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51049,7 +51049,7 @@
         <v>45359</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51122,7 +51122,7 @@
         <v>44895</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>44587</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51268,7 +51268,7 @@
         <v>46286</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45569</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>45588</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>45355</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51560,7 +51560,7 @@
         <v>44949</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51633,7 +51633,7 @@
         <v>46286</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>46197</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>46210</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45090</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51925,7 +51925,7 @@
         <v>44790</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>46244</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>46287</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         <v>44784</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>44935</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>44852</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52363,7 +52363,7 @@
         <v>45100</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>46288</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52514,7 +52514,7 @@
         <v>45517</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52587,7 +52587,7 @@
         <v>44578</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>44994</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>44900</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>45201</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>44966</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46288</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>46287</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>46287</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>46287</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46287</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>46288</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53400,7 +53400,7 @@
         <v>45323</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53473,7 +53473,7 @@
         <v>46287</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>46288</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         <v>45308</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53697,7 +53697,7 @@
         <v>45111</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45086</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53843,7 +53843,7 @@
         <v>45196</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45320</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>44987</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>45208</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>45001</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         <v>45901</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54281,7 +54281,7 @@
         <v>44585</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>45260</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>44992</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>44943</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54578,7 +54578,7 @@
         <v>45371</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54651,7 +54651,7 @@
         <v>46176</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54724,7 +54724,7 @@
         <v>46175</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54797,7 +54797,7 @@
         <v>44938</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54875,7 +54875,7 @@
         <v>44949</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54953,7 +54953,7 @@
         <v>45020</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45568</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55099,7 +55099,7 @@
         <v>46294</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>44894</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>44790</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55318,7 +55318,7 @@
         <v>44790</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>46254</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45211</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>44893</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>45174</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55683,7 +55683,7 @@
         <v>46253</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55756,7 +55756,7 @@
         <v>46253</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55829,7 +55829,7 @@
         <v>46297</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55902,7 +55902,7 @@
         <v>46296</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>44994</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45176</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45759</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56194,7 +56194,7 @@
         <v>45061</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56272,7 +56272,7 @@
         <v>46296</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45096</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         <v>46253</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56491,7 +56491,7 @@
         <v>46296</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56564,7 +56564,7 @@
         <v>46296</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>46204</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>46202</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>45391</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>45630</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45110</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45182</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57080,7 +57080,7 @@
         <v>45761</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         <v>45128</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57226,7 +57226,7 @@
         <v>45128</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57299,7 +57299,7 @@
         <v>44999</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         <v>45530</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45483</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>45271</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>45113</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57664,7 +57664,7 @@
         <v>44540</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>44916</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>45149</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57883,7 +57883,7 @@
         <v>45482</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57956,7 +57956,7 @@
         <v>44879</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58029,7 +58029,7 @@
         <v>45700</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>44603</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58175,7 +58175,7 @@
         <v>45147</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>44959</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58321,7 +58321,7 @@
         <v>45171</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58394,7 +58394,7 @@
         <v>45113</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>44967</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58540,7 +58540,7 @@
         <v>44963</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58613,7 +58613,7 @@
         <v>45720</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58686,7 +58686,7 @@
         <v>44909</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>45699</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>44784</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58905,7 +58905,7 @@
         <v>45243</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         <v>44643</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>45238</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59124,7 +59124,7 @@
         <v>44893</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45572</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45147</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45169</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59416,7 +59416,7 @@
         <v>44867</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>44745</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>45630</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>45533</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>45533</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45124</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59859,7 +59859,7 @@
         <v>45071</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59932,7 +59932,7 @@
         <v>45481</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60005,7 +60005,7 @@
         <v>45111</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60078,7 +60078,7 @@
         <v>45391</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         <v>45463</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>44237</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60297,7 +60297,7 @@
         <v>44981</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60375,7 +60375,7 @@
         <v>45351</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60448,7 +60448,7 @@
         <v>44992</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60521,7 +60521,7 @@
         <v>45224</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60594,7 +60594,7 @@
         <v>44587</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45415</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>44603</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60813,7 +60813,7 @@
         <v>45378</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60891,7 +60891,7 @@
         <v>45488</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>44474</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45488</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61110,7 +61110,7 @@
         <v>45114</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>45488</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61256,7 +61256,7 @@
         <v>45484</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61329,7 +61329,7 @@
         <v>45484</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61402,7 +61402,7 @@
         <v>44610</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>44853</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61548,7 +61548,7 @@
         <v>44602</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45761</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61699,7 +61699,7 @@
         <v>45832</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61772,7 +61772,7 @@
         <v>45840</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45840</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>45840</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45845</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>45848</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62137,7 +62137,7 @@
         <v>45884</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45978</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>46065</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62361,7 +62361,7 @@
         <v>46154</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62434,7 +62434,7 @@
         <v>46154</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62507,7 +62507,7 @@
         <v>46169</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62580,7 +62580,7 @@
         <v>46198</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62658,7 +62658,7 @@
         <v>46153</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62751,7 +62751,7 @@
         <v>46293</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>46293</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45121</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45377</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>45755</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45173</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>46302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45678</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45006</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45020</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>45979</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46100</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>45077</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>45742</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>45926</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>46300</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45378</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46145</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45674</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45008</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45760</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45168</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45168</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45048</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45786</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45072</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>46300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45761</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45415</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45224</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>45002</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45399</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>45104</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>45574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45959</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44991</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45649</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44600</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45818</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45667</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>46202</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>46274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>46238</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>46293</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46296</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>46300</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>46215</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>46300</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>46301</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45071</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45848</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>46073</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>44490</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>44481</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>44670</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>44480</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44824</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>44785</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44578</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44826</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44603</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>44588</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44862</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44494</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44483</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44542</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44512</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44790</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44530</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44588</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44588</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>44790</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44790</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44670</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>44729</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44774</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44733</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44733</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44480</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>44588</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44823</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44824</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44742</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44789</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44790</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44525</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44620</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44662</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44508</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44564</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44636</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44634</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44480</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44851</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44769</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44676</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44644</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>44612</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>44604</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>44517</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44819</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44854</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44621</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44876</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>44733</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>44866</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>44776</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45346</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44634</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45411</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45377</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>44966</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>44608</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44817</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45138</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>45211</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>44903</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>45097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45100</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45483</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45090</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45425</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45700</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44578</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45163</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>45090</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44867</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45453</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45245</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45450</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>44879</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>44963</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44903</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44944</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>44944</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>44896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>44890</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45250</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>44803</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>44588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45153</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45361</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45224</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45106</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45106</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44754</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>45100</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45699</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45308</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45299</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44517</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45110</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45539</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45630</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45224</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45224</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45196</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>44852</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45384</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>44607</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44949</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45558</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45114</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45121</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>44984</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45624</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45105</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45569</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45257</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44984</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45391</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45086</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45086</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45266</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45086</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45317</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>44833</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45215</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44789</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45309</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45350</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44720</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45359</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44488</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45482</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45369</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45371</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45371</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45359</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44553</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45554</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45722</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45635</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45545</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44861</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>45533</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45533</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45533</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45147</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45147</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45070</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45720</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>44991</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45884</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44964</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44994</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45149</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45169</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45278</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45456</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45243</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>44867</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45533</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45533</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45096</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45111</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44965</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44949</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45588</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>44967</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44875</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45171</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45171</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45030</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45581</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45475</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44510</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45061</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>44984</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44598</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>44938</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45481</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44510</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45483</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45498</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45891</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45891</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44879</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45301</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45301</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45475</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45901</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>45124</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45759</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45530</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45482</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45128</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45618</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45539</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45232</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45467</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45525</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45086</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45565</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45539</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>44918</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45257</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45378</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45498</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44893</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45018</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45607</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45275</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45540</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45301</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45513</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45513</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45110</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45000</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45415</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45552</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45098</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45391</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45111</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45481</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>44893</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45113</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45699</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44994</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45574</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44788</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45581</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45548</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45559</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45020</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45569</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45415</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45009</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45915</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44587</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45915</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45463</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45630</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44935</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44603</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44999</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44999</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45111</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44964</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45621</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45114</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45517</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44638</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45460</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45666</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45533</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45001</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44587</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44918</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44959</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45741</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>44966</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45495</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45726</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>44600</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45698</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45552</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45026</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45271</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>44910</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45567</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45554</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44585</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>45572</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45001</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>45930</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>45182</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45567</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45145</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45377</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44579</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45202</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44943</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>44643</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44944</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45603</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45328</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45713</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45527</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45574</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45715</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44992</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45394</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45071</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45934</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45635</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>44867</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45581</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45401</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>45533</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45804</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45804</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44784</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44795</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45168</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45052</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45176</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45805</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>45569</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44999</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45170</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44746</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>45623</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>44635</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45622</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45562</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45211</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45211</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>45075</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44784</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>45650</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45195</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45351</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45343</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45818</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45208</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45947</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45148</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>45121</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45818</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>45148</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45163</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45617</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45820</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45079</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45825</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>45254</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>45113</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45827</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44994</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>44958</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44965</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45334</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>44825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45128</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45832</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>45196</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>44973</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>45954</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>45959</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>45959</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45959</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45236</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>44663</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45961</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>45187</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45709</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45187</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>45707</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>45833</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>44977</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45835</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45837</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45610</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44894</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>44992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45020</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45840</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45308</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>45699</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>45174</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45832</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45114</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45041</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>45632</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>44745</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45722</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45615</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45820</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45761</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45299</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45971</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45811</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>45700</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45635</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45568</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45033</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45699</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45154</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45847</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45623</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>44790</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45260</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>44820</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45630</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44693</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45245</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45853</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45755</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45280</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45189</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>44956</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45317</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>45063</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>44769</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>45219</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>44546</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45646</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>45225</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>45237</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>45237</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45769</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>44988</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>44732</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45867</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45867</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45869</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45121</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>44502</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45870</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45870</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>44790</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>45323</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>45533</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45355</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45361</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45330</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>44839</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45217</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44578</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>44897</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45880</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45880</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45091</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45259</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45259</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45732</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>45090</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45090</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45349</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45201</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>44991</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>45113</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>45238</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44599</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45201</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45063</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42761,7 +42761,7 @@
         <v>45219</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>45674</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>46097</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45588</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45275</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>46099</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>44495</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>44848</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45440</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45985</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45754</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46105</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>44790</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>44861</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>44879</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45147</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>46101</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45114</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>44987</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45482</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45482</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45533</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45732</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45111</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>44910</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>44598</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>44931</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45027</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>45112</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45128</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>46111</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>46112</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>46112</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45481</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>44900</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>46112</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>46113</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>46113</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45394</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45029</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>46113</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>46112</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>46112</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>46112</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>46112</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>46113</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>46112</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45994</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>44857</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44585</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>44542</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>46121</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>44566</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>46125</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45743</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45261</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45048</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45503</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>46002</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>46002</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>44596</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>46128</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>44952</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45215</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44992</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45881</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>46136</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45919</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45224</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>44967</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>45804</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45867</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45867</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45834</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45632</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>46136</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45187</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45749</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45009</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45825</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45485</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45924</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45111</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45923</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>44910</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45658</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>44909</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>44964</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>46018</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49328,7 +49328,7 @@
         <v>45637</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>44832</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>46028</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45041</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44961</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49693,7 +49693,7 @@
         <v>46028</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>44916</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45805</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49912,7 +49912,7 @@
         <v>45300</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         <v>46030</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45245</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>46030</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>44999</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>46034</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         <v>45495</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50423,7 +50423,7 @@
         <v>45128</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45128</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45954</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>45320</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>46034</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>46035</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>46037</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>46037</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>46037</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>44613</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>46044</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45992</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51299,7 +51299,7 @@
         <v>46043</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51372,7 +51372,7 @@
         <v>44992</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45875</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>45875</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45768</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45028</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>45791</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45453</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45211</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>44540</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45174</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>44981</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>46057</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>46065</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52326,7 +52326,7 @@
         <v>46150</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>46083</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>46083</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>46104</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45981</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52691,7 +52691,7 @@
         <v>45867</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45755</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>46091</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>45961</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>46092</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53056,7 +53056,7 @@
         <v>46092</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53129,7 +53129,7 @@
         <v>46092</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>46175</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>46174</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>46176</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         <v>46176</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53494,7 +53494,7 @@
         <v>46181</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         <v>46183</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>46184</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>46186</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45985</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>46196</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53932,7 +53932,7 @@
         <v>46196</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>46198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>46203</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>46203</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54229,7 +54229,7 @@
         <v>46206</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54302,7 +54302,7 @@
         <v>46208</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54375,7 +54375,7 @@
         <v>46206</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45330</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>46213</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>46213</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>46213</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54740,7 +54740,7 @@
         <v>45897</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54813,7 +54813,7 @@
         <v>46216</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>46216</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>46216</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>46219</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>46219</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>46271</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>46272</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>46231</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>46272</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>46272</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>46230</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55616,7 +55616,7 @@
         <v>46274</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55689,7 +55689,7 @@
         <v>46272</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>46272</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55835,7 +55835,7 @@
         <v>46272</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>46274</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55981,7 +55981,7 @@
         <v>46276</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>46233</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>46232</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>46234</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
         <v>46275</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>46276</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>46275</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>46275</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>46276</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56638,7 +56638,7 @@
         <v>46275</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46280</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>46267</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>46280</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46237</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57003,7 +57003,7 @@
         <v>46279</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>46279</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>46238</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>46238</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
         <v>46238</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>46238</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>46234</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>46286</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>46197</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>46286</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>46287</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>46288</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>46287</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>46288</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>46288</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58113,7 +58113,7 @@
         <v>46244</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>46287</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>46287</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>46287</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>46288</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58483,7 +58483,7 @@
         <v>46287</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58556,7 +58556,7 @@
         <v>46210</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>46176</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>46175</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>44992</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58853,7 +58853,7 @@
         <v>46294</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58926,7 +58926,7 @@
         <v>45901</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>46296</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>46296</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>46253</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>46253</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>46296</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>46253</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>46256</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>46300</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>46300</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>46300</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>46296</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59807,7 +59807,7 @@
         <v>46256</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>46256</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>46204</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60031,7 +60031,7 @@
         <v>46254</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45952</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>46202</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60250,7 +60250,7 @@
         <v>46297</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>46259</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60396,7 +60396,7 @@
         <v>46301</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60469,7 +60469,7 @@
         <v>46301</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60542,7 +60542,7 @@
         <v>46301</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60615,7 +60615,7 @@
         <v>46301</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45526</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60766,7 +60766,7 @@
         <v>46303</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60839,7 +60839,7 @@
         <v>46303</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>45891</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>46303</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61058,7 +61058,7 @@
         <v>46303</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>46303</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61204,7 +61204,7 @@
         <v>44237</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61277,7 +61277,7 @@
         <v>44587</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>44603</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>44610</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>44602</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61569,7 +61569,7 @@
         <v>44981</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61647,7 +61647,7 @@
         <v>45351</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>44992</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>45224</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61866,7 +61866,7 @@
         <v>45415</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45378</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62017,7 +62017,7 @@
         <v>45488</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62090,7 +62090,7 @@
         <v>45488</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62163,7 +62163,7 @@
         <v>45114</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45488</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>45484</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>45484</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62455,7 +62455,7 @@
         <v>44853</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>45761</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>45832</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62679,7 +62679,7 @@
         <v>45840</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62752,7 +62752,7 @@
         <v>45840</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62825,7 +62825,7 @@
         <v>45840</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62898,7 +62898,7 @@
         <v>45845</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>45848</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>45884</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>45978</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>46065</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>46154</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>46154</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63414,7 +63414,7 @@
         <v>46169</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>46198</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -63565,7 +63565,7 @@
         <v>46153</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -63658,7 +63658,7 @@
         <v>46293</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -63731,7 +63731,7 @@
         <v>46293</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>44811</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45121</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>45377</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>45755</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>46175</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45173</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>46302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>45678</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45006</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45020</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>45979</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>46100</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>45077</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>45742</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>45926</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>46300</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>45378</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>46145</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45674</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45908</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>45008</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45760</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45168</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>45168</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>45048</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45786</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45072</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>46300</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>46300</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         <v>45378</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45484</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45761</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>44670</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45415</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45224</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
         <v>45002</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45399</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45125</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>45104</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>45574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45959</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>45979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44991</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45649</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44600</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45818</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>45667</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>46202</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>46274</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>46238</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>46293</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>46296</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>46300</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>46215</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>46300</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>46301</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>44803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45071</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45848</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>46073</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>44490</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>44481</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>44614</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>44670</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>44480</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44824</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>44785</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44578</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44516</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44826</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44603</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>44588</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44862</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44494</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44483</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44542</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44512</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44790</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44530</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44588</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44588</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>44790</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44790</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44670</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>44729</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44774</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44733</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44733</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44480</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>44588</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44823</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44824</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44742</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44789</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44790</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44854</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>44525</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>44620</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>44662</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>44508</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44564</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44636</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44634</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44480</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44817</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44851</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44769</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44676</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44644</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>44612</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>44604</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>44517</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44819</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44854</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44621</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44876</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>44733</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>44866</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13280,7 +13280,7 @@
         <v>44776</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45346</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44634</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>45411</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45377</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>44966</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>44608</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44817</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45138</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>45211</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>44903</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>45097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45100</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45483</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45090</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45425</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45700</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44578</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>45163</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>45090</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44867</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45453</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45245</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45450</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>44879</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>44963</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44903</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44944</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>44944</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>44896</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>44890</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45250</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>44803</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>44588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45153</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45361</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45224</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45106</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45106</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44754</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>45100</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45699</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45308</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>45299</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>44517</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45110</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45539</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45630</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45224</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45224</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45196</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>44852</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45384</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>44607</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44949</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45558</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45114</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45121</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>44984</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45624</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45105</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45569</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45257</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>44984</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45391</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45086</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45086</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45266</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45086</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45317</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>44833</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45215</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>44789</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45309</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45350</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44720</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45359</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>44488</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45482</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45369</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45371</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45371</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>44539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45359</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>44553</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45554</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45722</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45635</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45545</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>44861</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>45533</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>45533</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45533</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45147</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45147</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45070</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>45215</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45720</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>44991</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45884</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44964</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44994</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>45149</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45169</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45278</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45456</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21360,7 +21360,7 @@
         <v>45243</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45174</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>44867</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45533</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45533</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45096</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45111</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44965</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44949</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45588</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>44967</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>44875</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45171</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45171</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45030</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45581</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45475</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>44510</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45061</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>44984</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>44598</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>44938</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45481</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44510</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45483</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45498</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45891</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45891</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44879</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45301</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45301</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45475</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45901</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>45124</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45759</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45530</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45482</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45128</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45618</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45539</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45232</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45467</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45525</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45086</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45565</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45539</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>44918</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>45257</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45378</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45498</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44893</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45018</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>45607</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45275</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45540</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45301</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>45513</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>45513</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45110</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45000</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45415</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45552</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45098</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45391</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45111</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44630</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45481</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>44893</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45113</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45699</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44994</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45574</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44788</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45581</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45548</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45559</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45020</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45569</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45415</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45009</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45915</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44587</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45915</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45463</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45630</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44935</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44603</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44999</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44999</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45111</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44964</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45621</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45114</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45517</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44638</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45460</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45666</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>45533</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45001</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44587</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44918</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44959</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45741</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>44966</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45495</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45726</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>44600</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45698</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45552</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45026</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45271</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>44910</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>45567</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>45554</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>44585</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>45572</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45001</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>45930</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>45182</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45567</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45145</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45377</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44579</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45202</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44943</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>44643</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44944</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45603</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>45328</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45713</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45527</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45574</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45715</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44992</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45394</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>45071</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45934</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45635</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>44867</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45581</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45401</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>45533</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45804</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45804</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44784</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>44795</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45168</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45052</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45176</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45805</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>45569</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44999</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45170</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44746</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>45623</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>44635</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45622</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45562</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45211</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45211</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>45075</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44784</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33367,7 +33367,7 @@
         <v>45650</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45195</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>45351</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33586,7 +33586,7 @@
         <v>45343</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45818</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45208</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45947</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33883,7 +33883,7 @@
         <v>45148</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33956,7 +33956,7 @@
         <v>45121</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45818</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34112,7 +34112,7 @@
         <v>45148</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45163</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>45617</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45820</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34404,7 +34404,7 @@
         <v>45079</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34477,7 +34477,7 @@
         <v>44981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45825</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34623,7 +34623,7 @@
         <v>45254</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34701,7 +34701,7 @@
         <v>45113</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34774,7 +34774,7 @@
         <v>45827</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>44994</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>44958</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>44965</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45334</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>44825</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45128</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45832</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>45196</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35431,7 +35431,7 @@
         <v>44973</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35504,7 +35504,7 @@
         <v>45954</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35577,7 +35577,7 @@
         <v>45959</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35650,7 +35650,7 @@
         <v>45959</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>45959</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>45236</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>44663</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45961</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>45187</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45709</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45187</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36234,7 +36234,7 @@
         <v>45707</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>45833</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>44977</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45835</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>45837</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>45610</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44894</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>44992</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>45020</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45840</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45308</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>45699</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>45174</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45832</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45114</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45041</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>45632</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>44745</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45722</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45615</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45820</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45761</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>45299</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>45971</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45811</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>45700</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45635</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45568</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45033</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45699</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>45154</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45847</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45623</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>44790</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45260</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>44820</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45630</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44693</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45245</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45853</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45755</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45280</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45189</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>44956</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45317</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39534,7 +39534,7 @@
         <v>45063</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>44769</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39680,7 +39680,7 @@
         <v>45219</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>44546</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>45646</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39899,7 +39899,7 @@
         <v>45225</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39972,7 +39972,7 @@
         <v>45237</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>45237</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>45769</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>44988</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>44732</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40337,7 +40337,7 @@
         <v>45867</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45867</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45869</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45121</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>44502</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>45870</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>45870</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>44790</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>45323</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40994,7 +40994,7 @@
         <v>45533</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41067,7 +41067,7 @@
         <v>45355</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45361</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45330</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>44839</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45217</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44578</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>44897</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45880</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41656,7 +41656,7 @@
         <v>45880</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45091</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41802,7 +41802,7 @@
         <v>45259</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45259</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41958,7 +41958,7 @@
         <v>45732</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>45090</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42104,7 +42104,7 @@
         <v>45090</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>45349</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45201</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>44991</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>45113</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>45238</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>44599</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42615,7 +42615,7 @@
         <v>45201</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>45063</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42761,7 +42761,7 @@
         <v>45219</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>45674</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>46097</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45588</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45275</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>46099</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>44495</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>44848</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>45440</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45985</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45754</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46105</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>44790</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>44861</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>44879</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45147</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>46101</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45114</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>44987</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45482</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45482</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>45533</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45732</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45111</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>44910</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>44598</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>44931</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45027</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>45112</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44888,7 +44888,7 @@
         <v>45128</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>46111</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>46112</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>46112</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45481</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>44900</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>46112</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>46113</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>46113</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45394</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45029</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>46113</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>46112</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>46112</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>46112</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>46112</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46086,7 +46086,7 @@
         <v>46113</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>46112</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45994</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>44857</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46383,7 +46383,7 @@
         <v>44585</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46456,7 +46456,7 @@
         <v>44542</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46529,7 +46529,7 @@
         <v>46121</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>44566</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>46125</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
         <v>45743</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45261</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45048</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46967,7 +46967,7 @@
         <v>45503</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>46002</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47118,7 +47118,7 @@
         <v>46002</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>44596</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>46128</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>44952</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45215</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44992</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45881</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>46136</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>45919</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45224</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>44967</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>45804</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45867</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45867</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45834</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45632</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>46136</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>45187</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45749</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48525,7 +48525,7 @@
         <v>45009</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45825</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45485</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48744,7 +48744,7 @@
         <v>45924</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45111</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45923</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>44910</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49036,7 +49036,7 @@
         <v>45658</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>44909</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>44964</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49255,7 +49255,7 @@
         <v>46018</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49328,7 +49328,7 @@
         <v>45637</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>44832</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>46028</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45041</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44961</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49693,7 +49693,7 @@
         <v>46028</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>44916</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49839,7 +49839,7 @@
         <v>45805</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49912,7 +49912,7 @@
         <v>45300</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49985,7 +49985,7 @@
         <v>46030</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45245</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>46030</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>44999</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>46034</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         <v>45495</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50423,7 +50423,7 @@
         <v>45128</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>45128</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45954</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>45320</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>46034</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>46035</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>46037</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>46037</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>46037</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>44613</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>46044</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45992</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51299,7 +51299,7 @@
         <v>46043</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51372,7 +51372,7 @@
         <v>44992</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51445,7 +51445,7 @@
         <v>45875</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>45875</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45768</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51664,7 +51664,7 @@
         <v>45028</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51737,7 +51737,7 @@
         <v>45791</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51810,7 +51810,7 @@
         <v>45453</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45211</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>44540</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>45174</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>44981</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>46057</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52253,7 +52253,7 @@
         <v>46065</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52326,7 +52326,7 @@
         <v>46150</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         <v>46083</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52472,7 +52472,7 @@
         <v>46083</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52545,7 +52545,7 @@
         <v>46104</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>45981</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52691,7 +52691,7 @@
         <v>45867</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52764,7 +52764,7 @@
         <v>45755</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52837,7 +52837,7 @@
         <v>46091</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>45961</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>46092</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53056,7 +53056,7 @@
         <v>46092</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53129,7 +53129,7 @@
         <v>46092</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>46175</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>46174</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53348,7 +53348,7 @@
         <v>46176</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53421,7 +53421,7 @@
         <v>46176</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53494,7 +53494,7 @@
         <v>46181</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53567,7 +53567,7 @@
         <v>46183</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>46184</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>46186</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>45985</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>46196</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53932,7 +53932,7 @@
         <v>46196</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>46198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>46203</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>46203</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54229,7 +54229,7 @@
         <v>46206</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54302,7 +54302,7 @@
         <v>46208</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54375,7 +54375,7 @@
         <v>46206</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45330</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>46213</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>46213</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>46213</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54740,7 +54740,7 @@
         <v>45897</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54813,7 +54813,7 @@
         <v>46216</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54886,7 +54886,7 @@
         <v>46216</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>46216</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>46219</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>46219</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>46271</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55251,7 +55251,7 @@
         <v>46272</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>46231</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55397,7 +55397,7 @@
         <v>46272</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55470,7 +55470,7 @@
         <v>46272</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55543,7 +55543,7 @@
         <v>46230</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55616,7 +55616,7 @@
         <v>46274</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55689,7 +55689,7 @@
         <v>46272</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>46272</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55835,7 +55835,7 @@
         <v>46272</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>46274</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55981,7 +55981,7 @@
         <v>46276</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>46233</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56127,7 +56127,7 @@
         <v>46232</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>46234</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
         <v>46275</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56346,7 +56346,7 @@
         <v>46276</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56419,7 +56419,7 @@
         <v>46275</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56492,7 +56492,7 @@
         <v>46275</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56565,7 +56565,7 @@
         <v>46276</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56638,7 +56638,7 @@
         <v>46275</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46280</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>46267</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>46280</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46237</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57003,7 +57003,7 @@
         <v>46279</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57076,7 +57076,7 @@
         <v>46279</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57149,7 +57149,7 @@
         <v>46238</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>46238</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
         <v>46238</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>46238</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>46234</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>46286</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>46197</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>46286</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>46287</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>46288</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57884,7 +57884,7 @@
         <v>46287</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>46288</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58035,7 +58035,7 @@
         <v>46288</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58113,7 +58113,7 @@
         <v>46244</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>46287</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58259,7 +58259,7 @@
         <v>46287</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58332,7 +58332,7 @@
         <v>46287</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58405,7 +58405,7 @@
         <v>46288</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58483,7 +58483,7 @@
         <v>46287</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58556,7 +58556,7 @@
         <v>46210</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>46176</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>46175</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>44992</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58853,7 +58853,7 @@
         <v>46294</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58926,7 +58926,7 @@
         <v>45901</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>46296</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>46296</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>46253</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>46253</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>46296</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>46253</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>46256</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>46300</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>46300</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>46300</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>46296</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59807,7 +59807,7 @@
         <v>46256</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>46256</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59953,7 +59953,7 @@
         <v>46204</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60031,7 +60031,7 @@
         <v>46254</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60104,7 +60104,7 @@
         <v>45952</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60177,7 +60177,7 @@
         <v>46202</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60250,7 +60250,7 @@
         <v>46297</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>46259</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60396,7 +60396,7 @@
         <v>46301</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60469,7 +60469,7 @@
         <v>46301</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60542,7 +60542,7 @@
         <v>46301</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60615,7 +60615,7 @@
         <v>46301</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45526</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60766,7 +60766,7 @@
         <v>46303</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60839,7 +60839,7 @@
         <v>46303</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>45891</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>46303</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61058,7 +61058,7 @@
         <v>46303</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>46303</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61204,7 +61204,7 @@
         <v>44237</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61277,7 +61277,7 @@
         <v>44587</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>44603</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>44610</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>44602</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61569,7 +61569,7 @@
         <v>44981</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61647,7 +61647,7 @@
         <v>45351</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         <v>44992</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>45224</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61866,7 +61866,7 @@
         <v>45415</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61939,7 +61939,7 @@
         <v>45378</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62017,7 +62017,7 @@
         <v>45488</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62090,7 +62090,7 @@
         <v>45488</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62163,7 +62163,7 @@
         <v>45114</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62236,7 +62236,7 @@
         <v>45488</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62309,7 +62309,7 @@
         <v>45484</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62382,7 +62382,7 @@
         <v>45484</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62455,7 +62455,7 @@
         <v>44853</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>45761</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62606,7 +62606,7 @@
         <v>45832</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62679,7 +62679,7 @@
         <v>45840</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62752,7 +62752,7 @@
         <v>45840</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62825,7 +62825,7 @@
         <v>45840</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62898,7 +62898,7 @@
         <v>45845</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>45848</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>45884</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63122,7 +63122,7 @@
         <v>45978</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>46065</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>46154</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>46154</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63414,7 +63414,7 @@
         <v>46169</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>46198</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -63565,7 +63565,7 @@
         <v>46153</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -63658,7 +63658,7 @@
         <v>46293</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -63731,7 +63731,7 @@
         <v>46293</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>46310</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45777</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45377</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45301</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>46310</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>45173</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46302</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45678</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>46310</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45006</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45742</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45077</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45979</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45020</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>46100</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46300</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45378</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>46145</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45168</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45168</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45786</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45908</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45072</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>45674</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>46238</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45760</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>46300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>46300</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>45378</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45484</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45761</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>45104</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45224</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45002</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45667</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45818</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45125</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45959</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45399</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45415</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45649</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46202</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>46274</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>46238</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45574</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>46293</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>46296</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>46300</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>46300</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>46215</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>46301</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45071</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45848</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46073</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44614</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>44670</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44509</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44585</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>44824</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44785</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44826</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44862</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>44578</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44516</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44603</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44588</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>44542</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>44512</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>44790</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>44530</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>44588</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44790</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44790</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44670</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44729</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>44774</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44733</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44733</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44588</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44789</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44769</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44612</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44517</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>44819</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>44608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44525</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>44662</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44564</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>44817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44676</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44604</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>44854</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44823</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44790</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44854</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44620</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44722</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44644</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>44621</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44733</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>44609</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44776</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44634</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>44866</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44588</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44588</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45033</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45111</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45196</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44994</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45624</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45617</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44903</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45411</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44991</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45114</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>44991</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>44879</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44981</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>44693</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45261</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>44910</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>45346</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45732</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45610</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44992</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45052</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45453</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45394</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45299</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45623</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45020</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45552</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>44992</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45607</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45674</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45237</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45237</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45539</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45224</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45533</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44720</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44966</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45482</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44965</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45328</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45097</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>44931</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45558</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45309</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45254</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>45350</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>44861</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45300</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45063</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45145</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44981</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45187</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45217</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>44510</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>44566</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44488</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>44918</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>44553</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45030</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45450</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45275</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45168</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45552</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45460</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45187</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45163</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44988</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44754</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44613</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>44769</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45128</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45128</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45189</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45650</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45540</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45041</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45475</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45232</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45174</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45482</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45236</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45121</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>44867</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>44967</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45317</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>44944</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44944</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>44857</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45000</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>44965</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45359</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45467</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45440</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45554</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45495</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45425</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45257</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>44999</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>44789</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45301</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>44958</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45041</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45219</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44663</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45567</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45201</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45623</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45086</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44944</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44599</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45250</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45330</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45225</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45700</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44539</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44598</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45299</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45559</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>44848</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44910</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>45954</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45881</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45224</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>45658</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45884</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45415</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44542</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>46136</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44984</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45825</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45732</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45707</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44578</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45749</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45525</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>45875</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45875</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44964</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45891</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45891</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>46136</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45121</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45211</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45075</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44630</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45923</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45901</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45924</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45371</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45100</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45919</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45805</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>44795</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45632</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44964</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>44832</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45280</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45791</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45112</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45111</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45768</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45202</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45632</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45245</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>44585</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45170</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45915</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44867</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44732</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45635</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45483</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45713</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45615</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44984</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44984</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45018</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44788</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45930</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45070</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45934</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45028</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45456</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45481</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>44964</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45257</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>45533</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45533</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45001</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45569</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44879</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>46150</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45475</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44510</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>44961</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>44984</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>45090</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45174</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45091</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45947</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45646</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45954</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45959</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45959</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45545</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45361</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45959</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>44896</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>46104</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45867</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45961</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>45699</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45114</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>45111</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45111</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45098</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>45154</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>45722</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45481</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45453</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44502</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45755</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>45378</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45981</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45971</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>45377</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>45219</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45961</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44977</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45498</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>44825</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45215</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45533</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45754</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45187</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>44839</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44875</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45533</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>44973</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45985</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45106</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>45301</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>45722</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>45106</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>45743</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>45569</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>45148</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>45361</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>44952</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45548</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45394</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45138</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45317</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45384</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45994</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45513</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45513</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45637</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45153</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>46002</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45635</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45211</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         <v>44890</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>46002</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45278</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45029</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45588</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45699</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45086</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45128</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>44635</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45343</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45581</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45539</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45301</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44546</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46018</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45369</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>46174</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>46175</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>46176</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>46028</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>46028</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45741</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>46030</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>46030</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>46034</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45622</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45574</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45533</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>46176</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>46034</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>46035</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>46037</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46037</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>46037</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>46043</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46044</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>44833</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>44897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45498</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46181</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45009</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>44992</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46057</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>44999</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44999</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45148</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>46183</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>46184</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45581</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45495</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>45618</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45699</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>46065</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45259</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45259</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45562</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>45086</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>44517</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45533</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45121</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45275</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>44746</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>46186</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>44598</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45079</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46083</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46083</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>44579</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>44495</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45090</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45090</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>44638</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45985</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46091</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>46092</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>46092</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46097</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45245</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45415</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45621</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>46099</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>44861</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45308</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>46101</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45063</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44895</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45009</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>46196</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>46105</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>44820</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45215</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45215</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45351</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>46196</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>46198</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46111</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46112</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>46112</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>46112</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>46112</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46112</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>46112</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>46112</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>46112</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41395,7 +41395,7 @@
         <v>46113</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>46113</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41541,7 +41541,7 @@
         <v>46113</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>46113</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45539</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45565</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>46203</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>45482</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45195</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>45026</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>46121</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>45266</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>46125</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>46128</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45554</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44803</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45567</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>44587</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45110</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>44910</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45503</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45804</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>44956</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>44596</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46203</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45113</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45666</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44918</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45224</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45867</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45867</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45027</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45485</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45224</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>46208</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>45377</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45114</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>45330</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>46206</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45349</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45334</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45114</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>44600</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45581</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45359</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>44895</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44846,7 +44846,7 @@
         <v>44587</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>45569</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45588</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45355</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44949</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>46216</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46216</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46216</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>46213</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45090</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>45897</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>46213</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>46213</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44790</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>44784</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>46219</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>44935</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>44852</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>46219</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45100</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45517</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>44578</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>44994</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>44900</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45201</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>44966</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45323</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45308</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45111</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>46271</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>46272</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45086</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45196</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46230</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46231</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46272</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46272</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>46272</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>46272</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46272</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>46275</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45320</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>44987</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>46275</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>46274</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45208</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45001</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>44585</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45260</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44943</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>46232</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>46275</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>46274</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>46233</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45371</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46275</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>46276</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>44938</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>46276</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>46279</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>46234</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>44949</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>45020</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45568</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>46279</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>46276</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>46238</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>44894</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>46234</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>44790</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>44790</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>46238</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>46237</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45211</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>46238</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>44893</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45174</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>44994</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45176</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45759</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45061</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>46286</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45096</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45391</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>46286</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>46197</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>46210</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45630</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45110</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45182</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45761</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45128</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45128</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>44999</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>46244</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>46287</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>45530</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>45483</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>46288</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52239,7 +52239,7 @@
         <v>45271</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>45113</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>44540</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>44916</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>46288</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>46287</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>46287</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>46287</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>46287</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45149</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45482</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>46288</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>44879</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>46287</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>46288</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45700</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>44603</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45147</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>44959</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>45171</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>45113</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>44967</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53860,7 +53860,7 @@
         <v>45901</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>44992</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>44963</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45720</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         <v>44909</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>46176</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45699</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54376,7 +54376,7 @@
         <v>44784</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>46175</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>45243</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54595,7 +54595,7 @@
         <v>44643</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
         <v>45238</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>46294</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>44893</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45572</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45147</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45169</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>44867</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>46254</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>44745</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45630</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55398,7 +55398,7 @@
         <v>46253</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55471,7 +55471,7 @@
         <v>46253</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>46297</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55617,7 +55617,7 @@
         <v>45533</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55690,7 +55690,7 @@
         <v>45533</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45124</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>46296</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>46296</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>46253</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>46296</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>46296</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56206,7 +56206,7 @@
         <v>46204</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56284,7 +56284,7 @@
         <v>46202</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>46300</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45071</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>46256</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>46256</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56649,7 +56649,7 @@
         <v>45952</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45481</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56795,7 +56795,7 @@
         <v>45111</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         <v>45391</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>46301</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46300</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>46300</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>46301</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57238,7 +57238,7 @@
         <v>46301</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57311,7 +57311,7 @@
         <v>46256</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57384,7 +57384,7 @@
         <v>46301</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45463</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>46303</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57603,7 +57603,7 @@
         <v>46303</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45630</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>46303</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45698</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57895,7 +57895,7 @@
         <v>45726</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>45891</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58041,7 +58041,7 @@
         <v>46303</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>46303</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>46259</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>45526</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58338,7 +58338,7 @@
         <v>46307</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>46307</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>46307</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58557,7 +58557,7 @@
         <v>46307</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45527</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58703,7 +58703,7 @@
         <v>45603</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>45715</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>44992</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45574</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>45401</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>46308</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45635</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         <v>45804</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45804</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45805</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>46308</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>46308</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         <v>45818</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>45818</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59740,7 +59740,7 @@
         <v>45820</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>45825</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59886,7 +59886,7 @@
         <v>46267</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59959,7 +59959,7 @@
         <v>45827</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60032,7 +60032,7 @@
         <v>45833</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60105,7 +60105,7 @@
         <v>45832</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60178,7 +60178,7 @@
         <v>45709</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60251,7 +60251,7 @@
         <v>45835</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>45837</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60397,7 +60397,7 @@
         <v>45840</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60470,7 +60470,7 @@
         <v>45832</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60543,7 +60543,7 @@
         <v>45811</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60616,7 +60616,7 @@
         <v>45820</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60689,7 +60689,7 @@
         <v>45847</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>45853</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>45755</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60908,7 +60908,7 @@
         <v>45867</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45769</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61054,7 +61054,7 @@
         <v>45867</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45869</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61200,7 +61200,7 @@
         <v>45870</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         <v>45870</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61346,7 +61346,7 @@
         <v>45880</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45880</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>44237</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>44981</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61648,7 +61648,7 @@
         <v>45351</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>44992</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>45224</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>44587</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>45415</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62013,7 +62013,7 @@
         <v>44603</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>45378</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45488</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45488</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45114</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>45488</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>45484</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>45484</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>44610</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>44853</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>44602</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>45761</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45832</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45840</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>45840</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45840</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>45845</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>45848</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>45884</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>45978</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>46065</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>46154</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>46154</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>46169</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         <v>46198</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>46153</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -63951,7 +63951,7 @@
         <v>46293</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>46293</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>44939</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>46310</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45777</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45121</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45377</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45301</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>46310</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>45173</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>46302</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>45678</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>46310</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45006</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45742</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45926</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45077</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>45979</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>45020</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>46100</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>46300</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>45378</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>46145</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44943</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45168</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>45168</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45786</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45908</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>45072</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>45674</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>46205</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>46238</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45008</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45760</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45048</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>46300</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>46300</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>45378</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45484</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5725,7 +5725,7 @@
         <v>45761</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44670</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>44991</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>45104</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45224</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>45002</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44595</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>45070</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>45667</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45818</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45125</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>45959</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>45399</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45415</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>44600</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>45649</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46202</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>46274</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         <v>46238</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         <v>45574</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>46293</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8079,7 +8079,7 @@
         <v>46296</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>46300</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>46300</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>46215</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>46301</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44803</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>45071</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45848</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46073</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44490</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44614</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>44670</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44509</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44585</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>44824</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44785</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44826</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44862</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         <v>44578</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>44516</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>44603</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44588</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44494</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>44542</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>44512</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>44790</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>44530</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>44588</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44790</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44790</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44670</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44729</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>44774</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44733</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44733</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44588</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44789</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>44508</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44769</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>44612</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>44517</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>44819</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>44608</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44525</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>44662</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44564</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44636</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>44817</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44676</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44604</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>44854</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44823</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>44790</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>44854</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>44620</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44722</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44824</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44742</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44851</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         <v>44644</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>44621</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>44733</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>44609</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44776</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44634</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>44608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>44817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>44866</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44588</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44588</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45033</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45111</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45196</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13938,7 +13938,7 @@
         <v>44994</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45624</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14084,7 +14084,7 @@
         <v>45617</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>44607</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>44903</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45411</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44991</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45114</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>44991</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>44879</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45048</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>44981</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>44693</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45261</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>44910</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>45346</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45732</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>45147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>45610</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>44992</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>45052</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15549,7 +15549,7 @@
         <v>45453</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45394</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15695,7 +15695,7 @@
         <v>45299</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45623</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45020</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45552</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>44992</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45607</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>45674</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>45237</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45237</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16352,7 +16352,7 @@
         <v>45539</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45224</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45533</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>44720</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>44966</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45482</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>44965</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45328</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>45097</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>44931</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>45558</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45309</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45254</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>45350</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>44861</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45300</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>45063</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45145</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>44981</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45187</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>45217</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>44510</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>44566</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>44488</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>44918</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>44553</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45030</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45450</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45275</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45168</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45552</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45460</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45187</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45163</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44988</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>44754</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>44613</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>44769</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45128</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45128</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>45189</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45650</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45540</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45041</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45475</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45232</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45174</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45482</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45236</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45121</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>44867</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>44967</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44903</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45317</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>44944</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>44944</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>44857</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45000</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>44965</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20835,7 +20835,7 @@
         <v>45359</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20908,7 +20908,7 @@
         <v>45467</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45440</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45554</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45495</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45425</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         <v>45257</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21346,7 +21346,7 @@
         <v>44999</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21419,7 +21419,7 @@
         <v>44789</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21492,7 +21492,7 @@
         <v>45301</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21565,7 +21565,7 @@
         <v>44958</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45041</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45219</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>44663</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45567</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45201</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45623</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45086</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>44944</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44599</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45250</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45330</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45225</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22514,7 +22514,7 @@
         <v>45700</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22587,7 +22587,7 @@
         <v>44539</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44598</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45299</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45559</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>44848</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44910</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>45954</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45881</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45224</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>45658</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45884</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>45415</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44542</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>46136</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>44984</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45825</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45732</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45707</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>44578</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45749</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24130,7 +24130,7 @@
         <v>45525</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>45875</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>45875</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44964</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45891</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>45891</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>46136</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45121</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45211</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45075</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44630</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24938,7 +24938,7 @@
         <v>45923</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45901</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>45924</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45371</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>45100</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45919</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45805</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45834</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>44795</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45632</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44964</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>44832</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45280</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45791</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45112</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45111</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45768</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45202</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45632</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45245</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>44585</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45170</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>45915</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45915</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44867</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44732</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45635</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45483</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>45713</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45615</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27133,7 +27133,7 @@
         <v>44984</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44984</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45018</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27352,7 +27352,7 @@
         <v>45105</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44788</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27498,7 +27498,7 @@
         <v>45930</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27571,7 +27571,7 @@
         <v>45070</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45934</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45028</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45456</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45481</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27936,7 +27936,7 @@
         <v>44964</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45257</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28082,7 +28082,7 @@
         <v>45533</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         <v>45533</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45001</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45569</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>44879</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>46150</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45475</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28603,7 +28603,7 @@
         <v>44510</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28681,7 +28681,7 @@
         <v>44961</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>44984</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28827,7 +28827,7 @@
         <v>45090</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45174</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45091</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45947</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45646</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>45954</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45959</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>45959</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>45545</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45361</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45959</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>44896</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>46104</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45867</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45961</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>45699</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>45114</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>45111</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30141,7 +30141,7 @@
         <v>45111</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45098</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>45154</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30360,7 +30360,7 @@
         <v>45722</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45481</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>45453</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>44502</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30652,7 +30652,7 @@
         <v>45755</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>45378</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>45981</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45971</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>45377</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31017,7 +31017,7 @@
         <v>45219</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31168,7 +31168,7 @@
         <v>45961</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31241,7 +31241,7 @@
         <v>44977</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45498</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>44825</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31460,7 +31460,7 @@
         <v>45215</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31533,7 +31533,7 @@
         <v>45533</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45754</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45187</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>44839</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31825,7 +31825,7 @@
         <v>44875</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>45533</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>44973</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45985</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45106</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>45301</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32263,7 +32263,7 @@
         <v>45722</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32336,7 +32336,7 @@
         <v>45106</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>45743</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>45569</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32555,7 +32555,7 @@
         <v>45148</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32628,7 +32628,7 @@
         <v>45361</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>44952</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45548</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32847,7 +32847,7 @@
         <v>45394</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45138</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45317</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45384</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45994</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33217,7 +33217,7 @@
         <v>45513</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>45513</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33363,7 +33363,7 @@
         <v>45637</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45153</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33509,7 +33509,7 @@
         <v>46002</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45635</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45211</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         <v>44890</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>46002</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45278</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45029</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45588</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45699</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45086</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>45128</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>44635</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45343</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45581</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45539</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>45301</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>44546</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46018</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45369</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>46174</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>46175</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>46176</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>46028</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>46028</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45741</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>46030</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>46030</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>46034</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>45622</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45574</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45533</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>46176</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>46034</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>46035</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>46037</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46037</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>46037</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>46043</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46044</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>44833</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>44897</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45498</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46181</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45009</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>44992</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46057</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>44999</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>44999</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45148</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>46183</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>46184</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45581</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45495</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>45618</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45699</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>46065</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45259</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>45259</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45562</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37846,7 +37846,7 @@
         <v>45086</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>44517</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>45533</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>45121</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38143,7 +38143,7 @@
         <v>45275</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>44746</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>46186</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>44598</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45079</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46083</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>46083</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>44579</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>44495</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45090</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45090</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>44638</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45985</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>46091</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>46092</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>46092</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46097</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45245</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45415</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39530,7 +39530,7 @@
         <v>45621</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>46099</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>44861</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45308</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39822,7 +39822,7 @@
         <v>46101</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45063</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>44895</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>45009</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40114,7 +40114,7 @@
         <v>46196</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40187,7 +40187,7 @@
         <v>46105</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40260,7 +40260,7 @@
         <v>44820</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>45215</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45215</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45351</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>46196</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>46198</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
         <v>46111</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40776,7 +40776,7 @@
         <v>46112</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>46112</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>46112</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41010,7 +41010,7 @@
         <v>46112</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46112</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>46112</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41244,7 +41244,7 @@
         <v>46112</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>46112</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41395,7 +41395,7 @@
         <v>46113</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>46113</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41541,7 +41541,7 @@
         <v>46113</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>46113</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45539</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>45565</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>46203</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41906,7 +41906,7 @@
         <v>45482</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>45195</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>45026</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>46121</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42198,7 +42198,7 @@
         <v>45266</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>46125</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>46128</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45554</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44803</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45567</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>44587</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>45110</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>44910</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45503</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42928,7 +42928,7 @@
         <v>45804</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43001,7 +43001,7 @@
         <v>44956</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>44596</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>46203</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45113</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45666</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>44918</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45224</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45867</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>45867</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45027</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>45485</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>45224</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>46208</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>45377</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44116,7 +44116,7 @@
         <v>45114</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44189,7 +44189,7 @@
         <v>45330</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>46206</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45349</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44408,7 +44408,7 @@
         <v>45334</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44481,7 +44481,7 @@
         <v>45114</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44554,7 +44554,7 @@
         <v>44600</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45581</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45359</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44773,7 +44773,7 @@
         <v>44895</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44846,7 +44846,7 @@
         <v>44587</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44919,7 +44919,7 @@
         <v>45569</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44992,7 +44992,7 @@
         <v>45588</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45355</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44949</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45211,7 +45211,7 @@
         <v>46216</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45284,7 +45284,7 @@
         <v>46216</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>46216</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45430,7 +45430,7 @@
         <v>46213</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45090</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45576,7 +45576,7 @@
         <v>45897</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>46213</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>46213</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44790</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>44784</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45941,7 +45941,7 @@
         <v>46219</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>44935</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>44852</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>46219</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>45100</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45517</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>44578</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>44994</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>44900</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45201</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>44966</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45323</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45308</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45111</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>46271</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47036,7 +47036,7 @@
         <v>46272</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47109,7 +47109,7 @@
         <v>45086</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>45196</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46230</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46231</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46272</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>46272</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>46272</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>46272</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46272</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>46275</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45320</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>44987</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>46275</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>46274</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>45208</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45001</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>44585</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45260</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>44943</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>46232</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>46275</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>46274</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>46233</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>45371</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46275</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>46276</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>44938</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>46276</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49158,7 +49158,7 @@
         <v>46279</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>46234</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>44949</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>45020</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45568</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>46279</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>46276</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>46238</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>44894</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>46280</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>46234</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>44790</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>44790</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>46280</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>46238</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>46237</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45211</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>46238</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>44893</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45174</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>44994</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45176</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45759</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>45061</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         <v>46286</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45096</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45391</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>46286</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>46197</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>46210</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>45630</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51431,7 +51431,7 @@
         <v>45110</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45182</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51577,7 +51577,7 @@
         <v>45761</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45128</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45128</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>44999</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>46244</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>46287</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52015,7 +52015,7 @@
         <v>45530</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>45483</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>46288</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52239,7 +52239,7 @@
         <v>45271</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>45113</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>44540</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>44916</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>46288</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>46287</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>46287</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>46287</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>46287</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45149</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45482</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>46288</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>44879</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>46287</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>46288</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53349,7 +53349,7 @@
         <v>45700</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53422,7 +53422,7 @@
         <v>44603</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53495,7 +53495,7 @@
         <v>45147</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>44959</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53641,7 +53641,7 @@
         <v>45171</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53714,7 +53714,7 @@
         <v>45113</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53787,7 +53787,7 @@
         <v>44967</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53860,7 +53860,7 @@
         <v>45901</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>44992</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>44963</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45720</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         <v>44909</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>46176</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54303,7 +54303,7 @@
         <v>45699</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54376,7 +54376,7 @@
         <v>44784</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>46175</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54522,7 +54522,7 @@
         <v>45243</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54595,7 +54595,7 @@
         <v>44643</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
         <v>45238</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54741,7 +54741,7 @@
         <v>46294</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>44893</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45572</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45147</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55033,7 +55033,7 @@
         <v>45169</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55106,7 +55106,7 @@
         <v>44867</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55179,7 +55179,7 @@
         <v>46254</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55252,7 +55252,7 @@
         <v>44745</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55325,7 +55325,7 @@
         <v>45630</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55398,7 +55398,7 @@
         <v>46253</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55471,7 +55471,7 @@
         <v>46253</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>46297</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55617,7 +55617,7 @@
         <v>45533</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55690,7 +55690,7 @@
         <v>45533</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>45124</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>46296</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>46296</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55987,7 +55987,7 @@
         <v>46253</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>46296</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>46296</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56206,7 +56206,7 @@
         <v>46204</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56284,7 +56284,7 @@
         <v>46202</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56357,7 +56357,7 @@
         <v>46300</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56430,7 +56430,7 @@
         <v>45071</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>46256</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>46256</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56649,7 +56649,7 @@
         <v>45952</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56722,7 +56722,7 @@
         <v>45481</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56795,7 +56795,7 @@
         <v>45111</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56868,7 +56868,7 @@
         <v>45391</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56941,7 +56941,7 @@
         <v>46301</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57014,7 +57014,7 @@
         <v>46300</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57087,7 +57087,7 @@
         <v>46300</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>46301</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57238,7 +57238,7 @@
         <v>46301</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57311,7 +57311,7 @@
         <v>46256</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57384,7 +57384,7 @@
         <v>46301</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57457,7 +57457,7 @@
         <v>45463</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>46303</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57603,7 +57603,7 @@
         <v>46303</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57676,7 +57676,7 @@
         <v>45630</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57749,7 +57749,7 @@
         <v>46303</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57822,7 +57822,7 @@
         <v>45698</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57895,7 +57895,7 @@
         <v>45726</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57968,7 +57968,7 @@
         <v>45891</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58041,7 +58041,7 @@
         <v>46303</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>46303</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>46259</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>45526</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58338,7 +58338,7 @@
         <v>46307</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58411,7 +58411,7 @@
         <v>46307</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>46307</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58557,7 +58557,7 @@
         <v>46307</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>45527</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58703,7 +58703,7 @@
         <v>45603</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58776,7 +58776,7 @@
         <v>45715</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58849,7 +58849,7 @@
         <v>44992</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>45574</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58995,7 +58995,7 @@
         <v>45401</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>46308</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>45635</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59214,7 +59214,7 @@
         <v>45804</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45804</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59365,7 +59365,7 @@
         <v>45805</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59438,7 +59438,7 @@
         <v>46308</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59511,7 +59511,7 @@
         <v>46308</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59584,7 +59584,7 @@
         <v>45818</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>45818</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59740,7 +59740,7 @@
         <v>45820</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59813,7 +59813,7 @@
         <v>45825</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59886,7 +59886,7 @@
         <v>46267</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59959,7 +59959,7 @@
         <v>45827</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60032,7 +60032,7 @@
         <v>45833</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60105,7 +60105,7 @@
         <v>45832</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60178,7 +60178,7 @@
         <v>45709</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60251,7 +60251,7 @@
         <v>45835</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>45837</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60397,7 +60397,7 @@
         <v>45840</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60470,7 +60470,7 @@
         <v>45832</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60543,7 +60543,7 @@
         <v>45811</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60616,7 +60616,7 @@
         <v>45820</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60689,7 +60689,7 @@
         <v>45847</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>45853</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>45755</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60908,7 +60908,7 @@
         <v>45867</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45769</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61054,7 +61054,7 @@
         <v>45867</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61127,7 +61127,7 @@
         <v>45869</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61200,7 +61200,7 @@
         <v>45870</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         <v>45870</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61346,7 +61346,7 @@
         <v>45880</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45880</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>44237</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61570,7 +61570,7 @@
         <v>44981</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61648,7 +61648,7 @@
         <v>45351</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>44992</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61794,7 +61794,7 @@
         <v>45224</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>44587</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61940,7 +61940,7 @@
         <v>45415</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62013,7 +62013,7 @@
         <v>44603</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>45378</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45488</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45488</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45114</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>45488</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>45484</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>45484</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>44610</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>44853</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62748,7 +62748,7 @@
         <v>44602</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62821,7 +62821,7 @@
         <v>45761</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45832</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62972,7 +62972,7 @@
         <v>45840</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63045,7 +63045,7 @@
         <v>45840</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63118,7 +63118,7 @@
         <v>45840</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63191,7 +63191,7 @@
         <v>45845</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63264,7 +63264,7 @@
         <v>45848</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63337,7 +63337,7 @@
         <v>45884</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         <v>45978</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63488,7 +63488,7 @@
         <v>46065</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63561,7 +63561,7 @@
         <v>46154</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63634,7 +63634,7 @@
         <v>46154</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>46169</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -63780,7 +63780,7 @@
         <v>46198</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>46153</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -63951,7 +63951,7 @@
         <v>46293</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>46293</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>46310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45777</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45377</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>46238</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45301</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>46310</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45121</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45173</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>46302</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45678</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>46310</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45006</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>45979</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>45020</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>46300</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>46100</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>45742</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45926</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45077</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>45378</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>46145</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45908</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45674</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>46205</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>46238</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45072</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>46300</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>46300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>45786</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44943</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>45760</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>45168</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45168</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>45008</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5617,7 +5617,7 @@
         <v>45378</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>45484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45761</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44670</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>44600</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45959</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>45224</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>45070</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>46202</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>45002</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>45979</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>46238</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>46293</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>46296</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>46300</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>46215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>46300</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45649</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>46301</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45667</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>46314</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>46274</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>44991</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45415</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>45399</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45125</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>45104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45574</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44595</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>44803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>45071</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>45848</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>46073</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44614</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>44509</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44824</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>44585</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44785</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44826</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44578</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44516</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44603</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44588</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44542</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10277,7 +10277,7 @@
         <v>44512</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>44790</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44588</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44530</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44790</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>44790</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44670</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>44729</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44774</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44733</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>44733</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44588</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>44789</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44508</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>44769</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44612</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>44517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44819</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44608</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>44525</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44662</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44564</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>44636</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44817</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44676</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>44604</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>44854</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>44823</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>44854</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>44620</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>44790</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44722</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>44824</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>44742</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44851</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44621</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>44733</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>44609</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>44866</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>44776</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13426,7 +13426,7 @@
         <v>44634</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44608</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>44817</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>45483</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45090</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44967</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45891</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>45891</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45187</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>45009</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>45884</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45105</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45111</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>44833</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45215</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45901</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44909</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>44789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>45637</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>45411</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44961</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>44916</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45961</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45300</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45245</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44999</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45915</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45495</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45915</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>45128</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45128</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45320</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>44613</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45377</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44992</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45930</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>45211</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45097</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>45100</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>45028</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45453</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45211</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45934</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45425</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>44540</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45174</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>44981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45090</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>46174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45245</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45450</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>46176</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45138</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44895</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45308</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>45299</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>44895</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>46176</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>44852</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45384</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>45114</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>45257</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>45163</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>45947</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>46181</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45453</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>44963</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>44944</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45250</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>44803</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45153</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45954</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>46183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45106</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45699</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>46184</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45959</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45959</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45224</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45224</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>46186</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45959</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45961</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45558</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>44984</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45266</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45624</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44984</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>44984</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45317</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45350</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>45309</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45369</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45985</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>46196</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45554</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45722</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45635</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45545</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>46196</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45070</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45215</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45720</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44991</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46198</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>44994</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>45149</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45359</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45169</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45482</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45278</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45456</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45371</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45371</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45174</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45533</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45533</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45359</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>46203</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>46203</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>44965</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44875</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>44861</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45171</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45985</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>45533</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45533</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45533</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45475</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45061</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>44510</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45301</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45301</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45475</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>46208</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>46206</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45124</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45759</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45530</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45330</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45128</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46213</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>46213</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45147</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45147</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>46213</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45232</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45525</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45565</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45897</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45257</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>46216</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46216</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45018</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45607</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46216</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>45301</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45513</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>45513</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45110</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>46219</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45415</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>46219</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>45391</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26115,7 +26115,7 @@
         <v>45481</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>46002</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>46002</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>46231</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>46230</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>46233</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>46232</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>46234</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45463</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45630</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>46280</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46280</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46237</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46279</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>46279</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>46018</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46238</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46028</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45726</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>46028</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>46238</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45698</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>46234</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>46030</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>46030</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>46286</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>46034</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46034</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>46197</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>46035</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45243</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46037</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>46037</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>46037</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>46286</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46287</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46288</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>46044</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>46043</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46287</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>46288</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46244</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>46287</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>46287</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46287</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>46288</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46287</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45603</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>46210</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45527</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45574</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>45715</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>44992</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45635</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45401</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>45804</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45804</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>46176</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>45805</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>46057</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>46175</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>44992</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>45818</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>46294</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>46065</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45901</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45818</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>44949</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45820</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46296</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45825</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>46296</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>46253</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46083</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>45827</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>46083</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>46253</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>46296</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>46253</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>45832</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>46256</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>46300</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>46300</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>46300</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>45709</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32448,7 +32448,7 @@
         <v>46296</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>45833</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45835</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45171</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>46091</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45837</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>46256</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46256</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>46204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>46254</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33183,7 +33183,7 @@
         <v>45840</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33256,7 +33256,7 @@
         <v>46092</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>46092</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33402,7 +33402,7 @@
         <v>45832</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33475,7 +33475,7 @@
         <v>45952</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45030</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33621,7 +33621,7 @@
         <v>46202</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33694,7 +33694,7 @@
         <v>46097</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>46099</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33840,7 +33840,7 @@
         <v>44510</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44984</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45820</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>46297</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>44598</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44938</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45483</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45498</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45811</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>46105</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34575,7 +34575,7 @@
         <v>44879</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46259</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>46301</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34794,7 +34794,7 @@
         <v>45847</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>46101</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>46301</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>46301</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45853</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45755</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>45482</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>46111</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>46301</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35451,7 +35451,7 @@
         <v>46112</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35524,7 +35524,7 @@
         <v>46112</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35602,7 +35602,7 @@
         <v>46112</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>46113</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>46113</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>46113</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>46112</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         <v>46112</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>46112</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>46112</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>46113</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>46112</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45769</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45526</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45867</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45867</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45618</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45869</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45870</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45870</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>46303</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45467</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>46303</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37170,7 +37170,7 @@
         <v>45086</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>46121</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45891</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>46125</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37462,7 +37462,7 @@
         <v>46303</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         <v>46303</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>46303</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>44918</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45880</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37905,7 +37905,7 @@
         <v>46128</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45378</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>46307</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>46307</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38197,7 +38197,7 @@
         <v>45498</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38270,7 +38270,7 @@
         <v>44893</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>46308</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45275</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>45540</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>46308</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45881</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>46136</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>44630</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>44893</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45699</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39000,7 +39000,7 @@
         <v>44994</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39073,7 +39073,7 @@
         <v>45574</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>46307</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39219,7 +39219,7 @@
         <v>45919</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45224</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45559</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>45804</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45867</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45867</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>45834</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>46307</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45632</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>46308</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>46136</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>44587</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45749</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>44935</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>44603</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45825</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>44999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>44999</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45485</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45924</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40694,7 +40694,7 @@
         <v>45923</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>44964</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>44910</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45517</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40986,7 +40986,7 @@
         <v>44638</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41059,7 +41059,7 @@
         <v>45658</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44964</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46267</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41278,7 +41278,7 @@
         <v>45666</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41351,7 +41351,7 @@
         <v>46272</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>46272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>44832</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45805</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45001</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>44587</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>46271</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>44918</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>44959</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>46314</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>46314</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42154,7 +42154,7 @@
         <v>44644</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>44966</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42300,7 +42300,7 @@
         <v>45495</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>44600</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45954</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45026</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>44910</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45567</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>45554</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>45992</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>45875</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>45875</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43030,7 +43030,7 @@
         <v>46316</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>45768</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45567</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>45791</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>46316</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>45145</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>46315</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>46275</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>46276</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43687,7 +43687,7 @@
         <v>46272</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45202</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>46275</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43906,7 +43906,7 @@
         <v>46272</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>46274</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>46318</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>46274</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>46276</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>44943</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>44944</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44417,7 +44417,7 @@
         <v>46272</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>46272</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>45394</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>46275</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>46276</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>46275</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>44867</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>45581</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>45533</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45588</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>44784</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45176</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>46150</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45569</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44999</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45170</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>44746</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>45622</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>45562</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>45075</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>44784</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45343</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>46104</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46101,7 +46101,7 @@
         <v>45981</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45867</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45121</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46325,7 +46325,7 @@
         <v>45755</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45617</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>44981</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46544,7 +46544,7 @@
         <v>44994</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>44958</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46690,7 +46690,7 @@
         <v>44965</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46763,7 +46763,7 @@
         <v>45334</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46836,7 +46836,7 @@
         <v>44973</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>44977</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>45610</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>44894</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>44992</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>45020</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>45114</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47347,7 +47347,7 @@
         <v>45041</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45632</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>44745</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47566,7 +47566,7 @@
         <v>45615</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>45635</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45568</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45033</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45699</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>45154</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45630</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45189</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45063</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48223,7 +48223,7 @@
         <v>44769</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44546</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48369,7 +48369,7 @@
         <v>45646</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48442,7 +48442,7 @@
         <v>44988</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48515,7 +48515,7 @@
         <v>45121</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48588,7 +48588,7 @@
         <v>44502</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>45732</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45090</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45090</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48880,7 +48880,7 @@
         <v>45201</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48953,7 +48953,7 @@
         <v>44991</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49026,7 +49026,7 @@
         <v>45113</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>45238</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49172,7 +49172,7 @@
         <v>45063</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>45219</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49318,7 +49318,7 @@
         <v>45754</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45114</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45482</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45482</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45533</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>45732</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>45111</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>44910</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>44598</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>44931</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>45027</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>45112</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50204,7 +50204,7 @@
         <v>45029</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45346</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50350,7 +50350,7 @@
         <v>44966</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50423,7 +50423,7 @@
         <v>44903</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>44578</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>44867</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>44879</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50715,7 +50715,7 @@
         <v>44903</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50788,7 +50788,7 @@
         <v>44896</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50861,7 +50861,7 @@
         <v>44890</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>44588</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>44588</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>45361</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51153,7 +51153,7 @@
         <v>45224</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51231,7 +51231,7 @@
         <v>44754</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>45100</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         <v>44517</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51450,7 +51450,7 @@
         <v>45110</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51523,7 +51523,7 @@
         <v>45196</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>44607</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51669,7 +51669,7 @@
         <v>44949</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45121</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51825,7 +51825,7 @@
         <v>45569</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>45391</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51971,7 +51971,7 @@
         <v>45086</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52044,7 +52044,7 @@
         <v>45086</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52117,7 +52117,7 @@
         <v>45086</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>44720</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52263,7 +52263,7 @@
         <v>44539</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52336,7 +52336,7 @@
         <v>44553</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>44964</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52482,7 +52482,7 @@
         <v>44867</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>45096</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52628,7 +52628,7 @@
         <v>45111</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>45588</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52774,7 +52774,7 @@
         <v>44967</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>45581</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45481</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52993,7 +52993,7 @@
         <v>45539</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45539</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53139,7 +53139,7 @@
         <v>45000</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53212,7 +53212,7 @@
         <v>45552</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>45098</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45113</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>44788</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45581</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53577,7 +53577,7 @@
         <v>45548</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53650,7 +53650,7 @@
         <v>45020</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53723,7 +53723,7 @@
         <v>45569</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>45415</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53869,7 +53869,7 @@
         <v>45009</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53942,7 +53942,7 @@
         <v>45111</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54015,7 +54015,7 @@
         <v>45111</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54088,7 +54088,7 @@
         <v>45621</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>45114</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>45460</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54307,7 +54307,7 @@
         <v>45533</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>45741</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45552</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45271</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54604,7 +54604,7 @@
         <v>44585</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54677,7 +54677,7 @@
         <v>45572</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45001</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>45182</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>45377</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>44579</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55042,7 +55042,7 @@
         <v>44643</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45328</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45713</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>45071</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>44795</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>45168</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45052</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>45623</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55626,7 +55626,7 @@
         <v>44635</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>45211</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
         <v>45211</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55845,7 +55845,7 @@
         <v>45650</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         <v>45195</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55991,7 +55991,7 @@
         <v>45351</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>45208</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56137,7 +56137,7 @@
         <v>45148</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56210,7 +56210,7 @@
         <v>45148</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56283,7 +56283,7 @@
         <v>45163</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56356,7 +56356,7 @@
         <v>45079</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56429,7 +56429,7 @@
         <v>45254</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56507,7 +56507,7 @@
         <v>45113</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56580,7 +56580,7 @@
         <v>44825</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56653,7 +56653,7 @@
         <v>45128</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56726,7 +56726,7 @@
         <v>45196</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56799,7 +56799,7 @@
         <v>45236</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>44663</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>45187</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57018,7 +57018,7 @@
         <v>45187</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         <v>45707</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>45308</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45699</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45174</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57383,7 +57383,7 @@
         <v>45722</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57456,7 +57456,7 @@
         <v>45761</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57529,7 +57529,7 @@
         <v>45299</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57602,7 +57602,7 @@
         <v>45700</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57675,7 +57675,7 @@
         <v>45623</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57748,7 +57748,7 @@
         <v>44790</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57821,7 +57821,7 @@
         <v>45260</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57894,7 +57894,7 @@
         <v>44820</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>44693</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45245</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58118,7 +58118,7 @@
         <v>45280</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58191,7 +58191,7 @@
         <v>44956</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58269,7 +58269,7 @@
         <v>45317</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58347,7 +58347,7 @@
         <v>45219</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58420,7 +58420,7 @@
         <v>45225</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58493,7 +58493,7 @@
         <v>45237</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58566,7 +58566,7 @@
         <v>45237</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58639,7 +58639,7 @@
         <v>44732</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>44790</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>45323</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45533</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58931,7 +58931,7 @@
         <v>45355</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59004,7 +59004,7 @@
         <v>45361</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
         <v>45330</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>44839</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59223,7 +59223,7 @@
         <v>45217</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>44578</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59369,7 +59369,7 @@
         <v>44897</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>45091</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>45259</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59593,7 +59593,7 @@
         <v>45259</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>45349</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59744,7 +59744,7 @@
         <v>44599</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59817,7 +59817,7 @@
         <v>45201</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59890,7 +59890,7 @@
         <v>45674</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>45588</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60036,7 +60036,7 @@
         <v>45275</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60109,7 +60109,7 @@
         <v>44495</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60182,7 +60182,7 @@
         <v>44848</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60255,7 +60255,7 @@
         <v>45440</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60328,7 +60328,7 @@
         <v>44790</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60401,7 +60401,7 @@
         <v>44861</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60474,7 +60474,7 @@
         <v>44879</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60547,7 +60547,7 @@
         <v>45147</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60620,7 +60620,7 @@
         <v>44987</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60693,7 +60693,7 @@
         <v>45128</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60766,7 +60766,7 @@
         <v>45481</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60839,7 +60839,7 @@
         <v>44900</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>45394</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>44857</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61058,7 +61058,7 @@
         <v>44585</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61131,7 +61131,7 @@
         <v>44542</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61204,7 +61204,7 @@
         <v>44566</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61277,7 +61277,7 @@
         <v>45743</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>45261</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>45048</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>45503</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61569,7 +61569,7 @@
         <v>44596</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61642,7 +61642,7 @@
         <v>44952</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61715,7 +61715,7 @@
         <v>45215</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61788,7 +61788,7 @@
         <v>44992</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>44237</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61934,7 +61934,7 @@
         <v>44587</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62007,7 +62007,7 @@
         <v>44603</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62080,7 +62080,7 @@
         <v>44610</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62153,7 +62153,7 @@
         <v>44602</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62226,7 +62226,7 @@
         <v>44981</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62304,7 +62304,7 @@
         <v>45351</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62377,7 +62377,7 @@
         <v>44992</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62450,7 +62450,7 @@
         <v>45224</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62523,7 +62523,7 @@
         <v>45415</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62596,7 +62596,7 @@
         <v>45378</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62674,7 +62674,7 @@
         <v>45488</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62747,7 +62747,7 @@
         <v>45488</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62820,7 +62820,7 @@
         <v>45114</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62893,7 +62893,7 @@
         <v>45488</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62966,7 +62966,7 @@
         <v>45484</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63039,7 +63039,7 @@
         <v>45484</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63112,7 +63112,7 @@
         <v>44853</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63185,7 +63185,7 @@
         <v>45761</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63263,7 +63263,7 @@
         <v>45832</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63336,7 +63336,7 @@
         <v>45840</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>45840</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63482,7 +63482,7 @@
         <v>45840</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63555,7 +63555,7 @@
         <v>45845</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63628,7 +63628,7 @@
         <v>45848</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63701,7 +63701,7 @@
         <v>45884</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -63779,7 +63779,7 @@
         <v>45978</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -63852,7 +63852,7 @@
         <v>46065</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -63925,7 +63925,7 @@
         <v>46154</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -63998,7 +63998,7 @@
         <v>46154</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64071,7 +64071,7 @@
         <v>46169</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64144,7 +64144,7 @@
         <v>46198</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64222,7 +64222,7 @@
         <v>46153</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64315,7 +64315,7 @@
         <v>46293</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64388,7 +64388,7 @@
         <v>46293</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>

--- a/Översikt VIMMERBY.xlsx
+++ b/Översikt VIMMERBY.xlsx
@@ -601,7 +601,7 @@
         <v>44811</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44811</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>44950</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>44811</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>44811</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>46310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>44939</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45777</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44811</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>45755</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45377</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>46175</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>46238</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>45301</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>46310</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45121</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>45173</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>46302</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45678</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42993-2026</t>
+          <t>A 32348-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46310</v>
+        <v>46238</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2892,16 +2892,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>1</v>
@@ -2916,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2928,9 +2928,117 @@
         <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp
+Motaggsvamp
+Tallfingersvamp
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 32348-2026 artfynd.xlsx", "A 32348-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 32348-2026 karta.png", "A 32348-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 32348-2026 georefererad karta.tif", "A 32348-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 32348-2026 FSC-klagomål.docx", "A 32348-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 32348-2026 FSC-klagomål mail.docx", "A 32348-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 32348-2026 tillsynsbegäran.docx", "A 32348-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 32348-2026 tillsynsbegäran mail.docx", "A 32348-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 42993-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Brunfläckig pärlemorfjäril
 Jungfrulin
@@ -2938,107 +3046,107 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 42993-2026 artfynd.xlsx", "A 42993-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 42993-2026 karta.png", "A 42993-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 42993-2026 georefererad karta.tif", "A 42993-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 42993-2026 FSC-klagomål.docx", "A 42993-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 42993-2026 FSC-klagomål mail.docx", "A 42993-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 42993-2026 tillsynsbegäran.docx", "A 42993-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 42993-2026 tillsynsbegäran mail.docx", "A 42993-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>S 989-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45006</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>62</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>4</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>9</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Ullticka
@@ -3046,1477 +3154,1371 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/S 989-2023 artfynd.xlsx", "S 989-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/S 989-2023 karta.png", "S 989-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/S 989-2023 georefererad karta.tif", "S 989-2023")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/knärot/S 989-2023 karta knärot.png", "S 989-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/S 989-2023 FSC-klagomål.docx", "S 989-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/S 989-2023 FSC-klagomål mail.docx", "S 989-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/S 989-2023 tillsynsbegäran.docx", "S 989-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/S 989-2023 tillsynsbegäran mail.docx", "S 989-2023")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/fåglar/S 989-2023 prioriterade fågelarter.docx", "S 989-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 57053-2025</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45979</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="E24" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>2.1</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>2</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>2</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>7</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Aspfjädermossa
 Knärot
 Blåsippa</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 57053-2025 artfynd.xlsx", "A 57053-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 57053-2025 karta.png", "A 57053-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 57053-2025 georefererad karta.tif", "A 57053-2025")</f>
         <v/>
       </c>
-      <c r="Z23">
+      <c r="Z24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/knärot/A 57053-2025 karta knärot.png", "A 57053-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 57053-2025 FSC-klagomål.docx", "A 57053-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 57053-2025 FSC-klagomål mail.docx", "A 57053-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 57053-2025 tillsynsbegäran.docx", "A 57053-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 57053-2025 tillsynsbegäran mail.docx", "A 57053-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 15427-2023</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>45020</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>4.1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>4</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>3</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Slåtterfibbla
 Solvända
 Strävlosta</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 15427-2023 artfynd.xlsx", "A 15427-2023")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 15427-2023 karta.png", "A 15427-2023")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 15427-2023 georefererad karta.tif", "A 15427-2023")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 15427-2023 FSC-klagomål.docx", "A 15427-2023")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 15427-2023 FSC-klagomål mail.docx", "A 15427-2023")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 15427-2023 tillsynsbegäran.docx", "A 15427-2023")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 15427-2023 tillsynsbegäran mail.docx", "A 15427-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 41192-2026</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>46300</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>3.2</v>
       </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>3</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>4</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Guldlockmossa
 Platt fjädermossa
 Kransmossa</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 41192-2026 artfynd.xlsx", "A 41192-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 41192-2026 karta.png", "A 41192-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 41192-2026 georefererad karta.tif", "A 41192-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 41192-2026 FSC-klagomål.docx", "A 41192-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 41192-2026 FSC-klagomål mail.docx", "A 41192-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 41192-2026 tillsynsbegäran.docx", "A 41192-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 41192-2026 tillsynsbegäran mail.docx", "A 41192-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 14426-2026</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D27" s="1" t="n">
         <v>46100</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Kyrkan</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>8.6</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>3</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>3</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tallticka
 Linnea</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 14426-2026 artfynd.xlsx", "A 14426-2026")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 14426-2026 karta.png", "A 14426-2026")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 14426-2026 georefererad karta.tif", "A 14426-2026")</f>
         <v/>
       </c>
-      <c r="Z26">
+      <c r="Z27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/knärot/A 14426-2026 karta knärot.png", "A 14426-2026")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 14426-2026 FSC-klagomål.docx", "A 14426-2026")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 14426-2026 FSC-klagomål mail.docx", "A 14426-2026")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 14426-2026 tillsynsbegäran.docx", "A 14426-2026")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 14426-2026 tillsynsbegäran mail.docx", "A 14426-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 14584-2025</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
         <v>45742</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E28" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>5.4</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S28" t="n">
         <v>3</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T28" t="n">
         <v>4</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>4</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 14584-2025 artfynd.xlsx", "A 14584-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 14584-2025 karta.png", "A 14584-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 14584-2025 georefererad karta.tif", "A 14584-2025")</f>
         <v/>
       </c>
-      <c r="Z27">
+      <c r="Z28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/knärot/A 14584-2025 karta knärot.png", "A 14584-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 14584-2025 FSC-klagomål.docx", "A 14584-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 14584-2025 FSC-klagomål mail.docx", "A 14584-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 14584-2025 tillsynsbegäran.docx", "A 14584-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 14584-2025 tillsynsbegäran mail.docx", "A 14584-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/fåglar/A 14584-2025 prioriterade fågelarter.docx", "A 14584-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 46824-2025</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>45926</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="E29" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>2.8</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>2</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S29" t="n">
         <v>3</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>4</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Dropptaggsvamp
 Fjällig taggsvamp s.str.</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 46824-2025 artfynd.xlsx", "A 46824-2025")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 46824-2025 karta.png", "A 46824-2025")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 46824-2025 georefererad karta.tif", "A 46824-2025")</f>
         <v/>
       </c>
-      <c r="Z28">
+      <c r="Z29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/knärot/A 46824-2025 karta knärot.png", "A 46824-2025")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 46824-2025 FSC-klagomål.docx", "A 46824-2025")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 46824-2025 FSC-klagomål mail.docx", "A 46824-2025")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 46824-2025 tillsynsbegäran.docx", "A 46824-2025")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 46824-2025 tillsynsbegäran mail.docx", "A 46824-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 23602-2023</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>45077</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>1.6</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>2</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>3</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Vedtrappmossa
 Terpentinmossa
 Vanlig rörsvepemossa</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 23602-2023 artfynd.xlsx", "A 23602-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 23602-2023 karta.png", "A 23602-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 23602-2023 georefererad karta.tif", "A 23602-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 23602-2023 FSC-klagomål.docx", "A 23602-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 23602-2023 FSC-klagomål mail.docx", "A 23602-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 23602-2023 tillsynsbegäran.docx", "A 23602-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 23602-2023 tillsynsbegäran mail.docx", "A 23602-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>S 945-2024</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>45378</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="E31" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I31" t="n">
         <v>2.7</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>3</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>3</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Mosippa
 Knärot
 Dropptaggsvamp</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/S 945-2024 artfynd.xlsx", "S 945-2024")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/S 945-2024 karta.png", "S 945-2024")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/S 945-2024 georefererad karta.tif", "S 945-2024")</f>
         <v/>
       </c>
-      <c r="Z30">
+      <c r="Z31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/knärot/S 945-2024 karta knärot.png", "S 945-2024")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/S 945-2024 FSC-klagomål.docx", "S 945-2024")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/S 945-2024 FSC-klagomål mail.docx", "S 945-2024")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/S 945-2024 tillsynsbegäran.docx", "S 945-2024")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/S 945-2024 tillsynsbegäran mail.docx", "S 945-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>S 1260-2026</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D32" s="1" t="n">
         <v>46145</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
+      <c r="E32" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
         <v>5.3</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>4</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blåmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W31">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/S 1260-2026 artfynd.xlsx", "S 1260-2026")</f>
         <v/>
       </c>
-      <c r="X31">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/S 1260-2026 karta.png", "S 1260-2026")</f>
         <v/>
       </c>
-      <c r="Y31">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/S 1260-2026 georefererad karta.tif", "S 1260-2026")</f>
         <v/>
       </c>
-      <c r="Z31">
+      <c r="Z32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/knärot/S 1260-2026 karta knärot.png", "S 1260-2026")</f>
         <v/>
       </c>
-      <c r="AA31">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/S 1260-2026 FSC-klagomål.docx", "S 1260-2026")</f>
         <v/>
       </c>
-      <c r="AB31">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/S 1260-2026 FSC-klagomål mail.docx", "S 1260-2026")</f>
         <v/>
       </c>
-      <c r="AC31">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/S 1260-2026 tillsynsbegäran.docx", "S 1260-2026")</f>
         <v/>
       </c>
-      <c r="AD31">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/S 1260-2026 tillsynsbegäran mail.docx", "S 1260-2026")</f>
         <v/>
       </c>
-      <c r="AE31">
+      <c r="AE32">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/fåglar/S 1260-2026 prioriterade fågelarter.docx", "S 1260-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>A 42802-2025</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n">
+      <c r="D33" s="1" t="n">
         <v>45908</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
+      <c r="E33" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>2.8</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>2</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>2</v>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Tibast
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W32">
+      <c r="W33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 42802-2025 artfynd.xlsx", "A 42802-2025")</f>
         <v/>
       </c>
-      <c r="X32">
+      <c r="X33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 42802-2025 karta.png", "A 42802-2025")</f>
         <v/>
       </c>
-      <c r="Y32">
+      <c r="Y33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 42802-2025 georefererad karta.tif", "A 42802-2025")</f>
         <v/>
       </c>
-      <c r="AA32">
+      <c r="AA33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 42802-2025 FSC-klagomål.docx", "A 42802-2025")</f>
         <v/>
       </c>
-      <c r="AB32">
+      <c r="AB33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 42802-2025 FSC-klagomål mail.docx", "A 42802-2025")</f>
         <v/>
       </c>
-      <c r="AC32">
+      <c r="AC33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 42802-2025 tillsynsbegäran.docx", "A 42802-2025")</f>
         <v/>
       </c>
-      <c r="AD32">
+      <c r="AD33">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 42802-2025 tillsynsbegäran mail.docx", "A 42802-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>A 2604-2025</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="n">
         <v>45674</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
+      <c r="E34" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>7.6</v>
       </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>2</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>2</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>2</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>2</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>Långfibbla
 Spretfibbla</t>
         </is>
       </c>
-      <c r="W33">
+      <c r="W34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 2604-2025 artfynd.xlsx", "A 2604-2025")</f>
         <v/>
       </c>
-      <c r="X33">
+      <c r="X34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 2604-2025 karta.png", "A 2604-2025")</f>
         <v/>
       </c>
-      <c r="Y33">
+      <c r="Y34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 2604-2025 georefererad karta.tif", "A 2604-2025")</f>
         <v/>
       </c>
-      <c r="AA33">
+      <c r="AA34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 2604-2025 FSC-klagomål.docx", "A 2604-2025")</f>
         <v/>
       </c>
-      <c r="AB33">
+      <c r="AB34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 2604-2025 FSC-klagomål mail.docx", "A 2604-2025")</f>
         <v/>
       </c>
-      <c r="AC33">
+      <c r="AC34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 2604-2025 tillsynsbegäran.docx", "A 2604-2025")</f>
         <v/>
       </c>
-      <c r="AD33">
+      <c r="AD34">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 2604-2025 tillsynsbegäran mail.docx", "A 2604-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>A 29986-2026</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="n">
         <v>46205</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="E35" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>KALMAR LÄN</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>VIMMERBY</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.5</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>1</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>2</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S35" t="n">
         <v>2</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>2</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>Ask
 Gullpudra</t>
         </is>
       </c>
-      <c r="W34">
+      <c r="W35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 29986-2026 artfynd.xlsx", "A 29986-2026")</f>
         <v/>
       </c>
-      <c r="X34">
+      <c r="X35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 29986-2026 karta.png", "A 29986-2026")</f>
         <v/>
       </c>
-      <c r="Y34">
+      <c r="Y35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 29986-2026 georefererad karta.tif", "A 29986-2026")</f>
         <v/>
       </c>
-      <c r="AA34">
+      <c r="AA35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 29986-2026 FSC-klagomål.docx", "A 29986-2026")</f>
         <v/>
       </c>
-      <c r="AB34">
+      <c r="AB35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 29986-2026 FSC-klagomål mail.docx", "A 29986-2026")</f>
         <v/>
       </c>
-      <c r="AC34">
+      <c r="AC35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 29986-2026 tillsynsbegäran.docx", "A 29986-2026")</f>
         <v/>
       </c>
-      <c r="AD34">
+      <c r="AD35">
         <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 29986-2026 tillsynsbegäran mail.docx", "A 29986-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A 32348-2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>46320</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>KALMAR LÄN</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>VIMMERBY</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>Tallfingersvamp
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0884/artfynd/A 32348-2026 artfynd.xlsx", "A 32348-2026")</f>
-        <v/>
-      </c>
-      <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor/A 32348-2026 karta.png", "A 32348-2026")</f>
-        <v/>
-      </c>
-      <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0884/kartor_geotiff/A 32348-2026 georefererad karta.tif", "A 32348-2026")</f>
-        <v/>
-      </c>
-      <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomål/A 32348-2026 FSC-klagomål.docx", "A 32348-2026")</f>
-        <v/>
-      </c>
-      <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0884/klagomålsmail/A 32348-2026 FSC-klagomål mail.docx", "A 32348-2026")</f>
-        <v/>
-      </c>
-      <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsyn/A 32348-2026 tillsynsbegäran.docx", "A 32348-2026")</f>
-        <v/>
-      </c>
-      <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0884/tillsynsmail/A 32348-2026 tillsynsbegäran mail.docx", "A 32348-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
@@ -4537,7 +4539,7 @@
         <v>45072</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4643,7 +4645,7 @@
         <v>46300</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4749,7 +4751,7 @@
         <v>46300</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4855,7 +4857,7 @@
         <v>45786</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4965,7 +4967,7 @@
         <v>44943</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5075,7 +5077,7 @@
         <v>45760</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5181,7 +5183,7 @@
         <v>45168</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5291,7 +5293,7 @@
         <v>45168</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5401,7 +5403,7 @@
         <v>45048</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5511,7 +5513,7 @@
         <v>45008</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5617,7 +5619,7 @@
         <v>45378</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5728,7 +5730,7 @@
         <v>45484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5834,7 +5836,7 @@
         <v>45761</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5949,7 +5951,7 @@
         <v>44670</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6054,7 +6056,7 @@
         <v>44600</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6159,7 +6161,7 @@
         <v>45959</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6268,7 +6270,7 @@
         <v>45224</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6373,7 +6375,7 @@
         <v>45070</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6478,7 +6480,7 @@
         <v>46202</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6583,7 +6585,7 @@
         <v>45002</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6688,7 +6690,7 @@
         <v>45979</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6802,7 +6804,7 @@
         <v>46238</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6907,7 +6909,7 @@
         <v>46293</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7012,7 +7014,7 @@
         <v>46296</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7122,7 +7124,7 @@
         <v>46300</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7231,7 +7233,7 @@
         <v>46215</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7336,7 +7338,7 @@
         <v>46300</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7445,7 +7447,7 @@
         <v>45649</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7554,7 +7556,7 @@
         <v>46301</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7659,7 +7661,7 @@
         <v>45818</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7769,7 +7771,7 @@
         <v>45667</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7878,7 +7880,7 @@
         <v>46314</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7987,7 +7989,7 @@
         <v>46274</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8092,7 +8094,7 @@
         <v>44991</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8201,7 +8203,7 @@
         <v>45415</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8306,7 +8308,7 @@
         <v>45399</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8411,7 +8413,7 @@
         <v>45125</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8516,7 +8518,7 @@
         <v>45104</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8621,7 +8623,7 @@
         <v>45574</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8730,7 +8732,7 @@
         <v>44595</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8835,7 +8837,7 @@
         <v>44803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8940,7 +8942,7 @@
         <v>45071</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9045,7 +9047,7 @@
         <v>45848</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9150,7 +9152,7 @@
         <v>46073</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9255,7 +9257,7 @@
         <v>44614</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9328,7 +9330,7 @@
         <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9401,7 +9403,7 @@
         <v>44509</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9474,7 +9476,7 @@
         <v>44824</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9547,7 +9549,7 @@
         <v>44585</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9620,7 +9622,7 @@
         <v>44785</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9693,7 +9695,7 @@
         <v>44826</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9766,7 +9768,7 @@
         <v>44578</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9839,7 +9841,7 @@
         <v>44516</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9912,7 +9914,7 @@
         <v>44862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9985,7 +9987,7 @@
         <v>44603</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10058,7 +10060,7 @@
         <v>44588</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10131,7 +10133,7 @@
         <v>44542</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10204,7 +10206,7 @@
         <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10277,7 +10279,7 @@
         <v>44512</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10350,7 +10352,7 @@
         <v>44790</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10423,7 +10425,7 @@
         <v>44588</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10496,7 +10498,7 @@
         <v>44588</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10569,7 +10571,7 @@
         <v>44530</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10642,7 +10644,7 @@
         <v>44790</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10715,7 +10717,7 @@
         <v>44790</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10788,7 +10790,7 @@
         <v>44670</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10861,7 +10863,7 @@
         <v>44729</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10934,7 +10936,7 @@
         <v>44774</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11007,7 +11009,7 @@
         <v>44733</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11080,7 +11082,7 @@
         <v>44733</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11153,7 +11155,7 @@
         <v>44588</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11226,7 +11228,7 @@
         <v>44789</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11299,7 +11301,7 @@
         <v>44508</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11377,7 +11379,7 @@
         <v>44634</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11450,7 +11452,7 @@
         <v>44769</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11523,7 +11525,7 @@
         <v>44612</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11596,7 +11598,7 @@
         <v>44517</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11669,7 +11671,7 @@
         <v>44819</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11742,7 +11744,7 @@
         <v>44608</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11815,7 +11817,7 @@
         <v>44525</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11888,7 +11890,7 @@
         <v>44662</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11961,7 +11963,7 @@
         <v>44564</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12034,7 +12036,7 @@
         <v>44636</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12107,7 +12109,7 @@
         <v>44817</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12180,7 +12182,7 @@
         <v>44676</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12253,7 +12255,7 @@
         <v>44604</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12326,7 +12328,7 @@
         <v>44854</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12399,7 +12401,7 @@
         <v>44823</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12472,7 +12474,7 @@
         <v>44854</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12545,7 +12547,7 @@
         <v>44620</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12618,7 +12620,7 @@
         <v>44790</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12691,7 +12693,7 @@
         <v>44722</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12764,7 +12766,7 @@
         <v>44824</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12837,7 +12839,7 @@
         <v>44742</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12910,7 +12912,7 @@
         <v>44851</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12983,7 +12985,7 @@
         <v>44621</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13056,7 +13058,7 @@
         <v>44876</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13129,7 +13131,7 @@
         <v>44733</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13202,7 +13204,7 @@
         <v>44609</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13275,7 +13277,7 @@
         <v>44866</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13353,7 +13355,7 @@
         <v>44776</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13426,7 +13428,7 @@
         <v>44634</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13499,7 +13501,7 @@
         <v>44608</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13572,7 +13574,7 @@
         <v>44817</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13645,7 +13647,7 @@
         <v>45483</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13718,7 +13720,7 @@
         <v>45090</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13791,7 +13793,7 @@
         <v>44967</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13864,7 +13866,7 @@
         <v>45891</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13937,7 +13939,7 @@
         <v>45891</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14010,7 +14012,7 @@
         <v>45187</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14083,7 +14085,7 @@
         <v>45009</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14156,7 +14158,7 @@
         <v>45884</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14234,7 +14236,7 @@
         <v>45105</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14307,7 +14309,7 @@
         <v>45111</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14380,7 +14382,7 @@
         <v>44833</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14453,7 +14455,7 @@
         <v>45215</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14526,7 +14528,7 @@
         <v>45901</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14599,7 +14601,7 @@
         <v>44909</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14672,7 +14674,7 @@
         <v>44789</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14745,7 +14747,7 @@
         <v>45637</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14818,7 +14820,7 @@
         <v>45411</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14891,7 +14893,7 @@
         <v>45041</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14964,7 +14966,7 @@
         <v>44961</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15037,7 +15039,7 @@
         <v>44916</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15110,7 +15112,7 @@
         <v>45961</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15183,7 +15185,7 @@
         <v>45300</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15256,7 +15258,7 @@
         <v>45245</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15329,7 +15331,7 @@
         <v>44999</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15402,7 +15404,7 @@
         <v>45915</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15475,7 +15477,7 @@
         <v>45495</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15548,7 +15550,7 @@
         <v>45915</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15621,7 +15623,7 @@
         <v>45128</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15694,7 +15696,7 @@
         <v>45128</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15767,7 +15769,7 @@
         <v>45320</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15840,7 +15842,7 @@
         <v>44613</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15913,7 +15915,7 @@
         <v>45377</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15986,7 +15988,7 @@
         <v>44992</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16059,7 +16061,7 @@
         <v>45930</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16132,7 +16134,7 @@
         <v>45211</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16205,7 +16207,7 @@
         <v>45097</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16283,7 +16285,7 @@
         <v>45100</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16356,7 +16358,7 @@
         <v>45028</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16429,7 +16431,7 @@
         <v>45453</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16502,7 +16504,7 @@
         <v>45211</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16580,7 +16582,7 @@
         <v>45934</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16653,7 +16655,7 @@
         <v>45425</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16726,7 +16728,7 @@
         <v>44540</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16799,7 +16801,7 @@
         <v>45174</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16872,7 +16874,7 @@
         <v>44981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16945,7 +16947,7 @@
         <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17018,7 +17020,7 @@
         <v>45090</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17091,7 +17093,7 @@
         <v>46174</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17164,7 +17166,7 @@
         <v>45245</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17237,7 +17239,7 @@
         <v>45450</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17310,7 +17312,7 @@
         <v>46176</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17383,7 +17385,7 @@
         <v>45138</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17456,7 +17458,7 @@
         <v>44895</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17529,7 +17531,7 @@
         <v>45308</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17602,7 +17604,7 @@
         <v>45299</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17675,7 +17677,7 @@
         <v>45539</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17748,7 +17750,7 @@
         <v>44895</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17821,7 +17823,7 @@
         <v>46176</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17894,7 +17896,7 @@
         <v>44852</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17967,7 +17969,7 @@
         <v>45384</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18040,7 +18042,7 @@
         <v>45700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18113,7 +18115,7 @@
         <v>45114</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18186,7 +18188,7 @@
         <v>45257</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18259,7 +18261,7 @@
         <v>45163</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18332,7 +18334,7 @@
         <v>45947</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18405,7 +18407,7 @@
         <v>46181</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18478,7 +18480,7 @@
         <v>45453</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18551,7 +18553,7 @@
         <v>44963</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18624,7 +18626,7 @@
         <v>44944</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18697,7 +18699,7 @@
         <v>45250</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18770,7 +18772,7 @@
         <v>44803</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18843,7 +18845,7 @@
         <v>45153</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18916,7 +18918,7 @@
         <v>45954</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18989,7 +18991,7 @@
         <v>46183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19062,7 +19064,7 @@
         <v>45106</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19135,7 +19137,7 @@
         <v>45106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19208,7 +19210,7 @@
         <v>45699</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19281,7 +19283,7 @@
         <v>46184</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19354,7 +19356,7 @@
         <v>45959</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19427,7 +19429,7 @@
         <v>45630</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19500,7 +19502,7 @@
         <v>45959</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19573,7 +19575,7 @@
         <v>45224</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19646,7 +19648,7 @@
         <v>45224</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19724,7 +19726,7 @@
         <v>46186</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19797,7 +19799,7 @@
         <v>45959</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19870,7 +19872,7 @@
         <v>45961</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19943,7 +19945,7 @@
         <v>45558</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20016,7 +20018,7 @@
         <v>44984</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20089,7 +20091,7 @@
         <v>45266</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20162,7 +20164,7 @@
         <v>45624</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20235,7 +20237,7 @@
         <v>44984</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20308,7 +20310,7 @@
         <v>44984</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20381,7 +20383,7 @@
         <v>45317</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20459,7 +20461,7 @@
         <v>45350</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20532,7 +20534,7 @@
         <v>45309</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20605,7 +20607,7 @@
         <v>45369</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20678,7 +20680,7 @@
         <v>45985</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20751,7 +20753,7 @@
         <v>45971</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20824,7 +20826,7 @@
         <v>46196</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20897,7 +20899,7 @@
         <v>45554</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20970,7 +20972,7 @@
         <v>45722</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21043,7 +21045,7 @@
         <v>45635</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21116,7 +21118,7 @@
         <v>45545</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21189,7 +21191,7 @@
         <v>46196</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21262,7 +21264,7 @@
         <v>45070</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21335,7 +21337,7 @@
         <v>45215</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21408,7 +21410,7 @@
         <v>45720</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21481,7 +21483,7 @@
         <v>44991</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21554,7 +21556,7 @@
         <v>46198</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21632,7 +21634,7 @@
         <v>44994</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21705,7 +21707,7 @@
         <v>45149</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21778,7 +21780,7 @@
         <v>45359</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21851,7 +21853,7 @@
         <v>45169</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21924,7 +21926,7 @@
         <v>45482</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21997,7 +21999,7 @@
         <v>45278</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22075,7 +22077,7 @@
         <v>45456</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22148,7 +22150,7 @@
         <v>45371</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22221,7 +22223,7 @@
         <v>45371</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22294,7 +22296,7 @@
         <v>45174</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22367,7 +22369,7 @@
         <v>45533</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22440,7 +22442,7 @@
         <v>45533</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22518,7 +22520,7 @@
         <v>45359</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22591,7 +22593,7 @@
         <v>46203</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22664,7 +22666,7 @@
         <v>46203</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22737,7 +22739,7 @@
         <v>44965</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22810,7 +22812,7 @@
         <v>44875</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22883,7 +22885,7 @@
         <v>44861</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22956,7 +22958,7 @@
         <v>45171</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23029,7 +23031,7 @@
         <v>45985</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23102,7 +23104,7 @@
         <v>45533</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23175,7 +23177,7 @@
         <v>45533</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23253,7 +23255,7 @@
         <v>45533</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23331,7 +23333,7 @@
         <v>45475</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23404,7 +23406,7 @@
         <v>45061</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23482,7 +23484,7 @@
         <v>44510</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23560,7 +23562,7 @@
         <v>45301</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23633,7 +23635,7 @@
         <v>45301</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23706,7 +23708,7 @@
         <v>45475</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23779,7 +23781,7 @@
         <v>46208</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23852,7 +23854,7 @@
         <v>46206</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23925,7 +23927,7 @@
         <v>45124</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23998,7 +24000,7 @@
         <v>45759</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24071,7 +24073,7 @@
         <v>45530</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24144,7 +24146,7 @@
         <v>45330</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24217,7 +24219,7 @@
         <v>45128</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24290,7 +24292,7 @@
         <v>46213</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24363,7 +24365,7 @@
         <v>46213</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24436,7 +24438,7 @@
         <v>45994</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24509,7 +24511,7 @@
         <v>45147</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24582,7 +24584,7 @@
         <v>45147</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24655,7 +24657,7 @@
         <v>46213</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24728,7 +24730,7 @@
         <v>45232</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24801,7 +24803,7 @@
         <v>45525</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24874,7 +24876,7 @@
         <v>45565</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24947,7 +24949,7 @@
         <v>45897</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25020,7 +25022,7 @@
         <v>45257</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25093,7 +25095,7 @@
         <v>46216</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25166,7 +25168,7 @@
         <v>46216</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25239,7 +25241,7 @@
         <v>45018</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25312,7 +25314,7 @@
         <v>45607</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25385,7 +25387,7 @@
         <v>46216</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25458,7 +25460,7 @@
         <v>45301</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25531,7 +25533,7 @@
         <v>45513</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25604,7 +25606,7 @@
         <v>45513</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25677,7 +25679,7 @@
         <v>45110</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25750,7 +25752,7 @@
         <v>46219</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25823,7 +25825,7 @@
         <v>45415</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25896,7 +25898,7 @@
         <v>46219</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25969,7 +25971,7 @@
         <v>45391</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26042,7 +26044,7 @@
         <v>45111</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26115,7 +26117,7 @@
         <v>45481</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26188,7 +26190,7 @@
         <v>46002</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26266,7 +26268,7 @@
         <v>46002</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26344,7 +26346,7 @@
         <v>46231</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26417,7 +26419,7 @@
         <v>46230</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26490,7 +26492,7 @@
         <v>46233</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26563,7 +26565,7 @@
         <v>46232</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26636,7 +26638,7 @@
         <v>46234</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26709,7 +26711,7 @@
         <v>45463</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26782,7 +26784,7 @@
         <v>45630</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26855,7 +26857,7 @@
         <v>46280</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26928,7 +26930,7 @@
         <v>46280</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27001,7 +27003,7 @@
         <v>46237</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27074,7 +27076,7 @@
         <v>46279</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27147,7 +27149,7 @@
         <v>46279</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27220,7 +27222,7 @@
         <v>46018</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27293,7 +27295,7 @@
         <v>46238</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27366,7 +27368,7 @@
         <v>46028</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27439,7 +27441,7 @@
         <v>45726</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27512,7 +27514,7 @@
         <v>46028</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27585,7 +27587,7 @@
         <v>46238</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27658,7 +27660,7 @@
         <v>45698</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27731,7 +27733,7 @@
         <v>46234</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27804,7 +27806,7 @@
         <v>46030</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27877,7 +27879,7 @@
         <v>46030</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27950,7 +27952,7 @@
         <v>46286</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28023,7 +28025,7 @@
         <v>46034</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28096,7 +28098,7 @@
         <v>46034</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28169,7 +28171,7 @@
         <v>46197</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28242,7 +28244,7 @@
         <v>46035</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28315,7 +28317,7 @@
         <v>45243</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28388,7 +28390,7 @@
         <v>46037</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28461,7 +28463,7 @@
         <v>46037</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28534,7 +28536,7 @@
         <v>46037</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28607,7 +28609,7 @@
         <v>46286</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28680,7 +28682,7 @@
         <v>46287</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28753,7 +28755,7 @@
         <v>46288</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28831,7 +28833,7 @@
         <v>46044</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28904,7 +28906,7 @@
         <v>46043</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28977,7 +28979,7 @@
         <v>46287</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29050,7 +29052,7 @@
         <v>46288</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29128,7 +29130,7 @@
         <v>46288</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29206,7 +29208,7 @@
         <v>46244</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29279,7 +29281,7 @@
         <v>46287</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29352,7 +29354,7 @@
         <v>46287</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29425,7 +29427,7 @@
         <v>46287</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29498,7 +29500,7 @@
         <v>46288</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29576,7 +29578,7 @@
         <v>46287</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29649,7 +29651,7 @@
         <v>45603</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29722,7 +29724,7 @@
         <v>46210</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29795,7 +29797,7 @@
         <v>45527</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29868,7 +29870,7 @@
         <v>45574</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29941,7 +29943,7 @@
         <v>45715</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30014,7 +30016,7 @@
         <v>44992</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30087,7 +30089,7 @@
         <v>45635</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30160,7 +30162,7 @@
         <v>45401</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30233,7 +30235,7 @@
         <v>45804</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30311,7 +30313,7 @@
         <v>45804</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30384,7 +30386,7 @@
         <v>46176</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30457,7 +30459,7 @@
         <v>45805</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30530,7 +30532,7 @@
         <v>46057</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30603,7 +30605,7 @@
         <v>46175</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30676,7 +30678,7 @@
         <v>44992</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30754,7 +30756,7 @@
         <v>45818</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30832,7 +30834,7 @@
         <v>46294</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30905,7 +30907,7 @@
         <v>46065</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30978,7 +30980,7 @@
         <v>45901</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31051,7 +31053,7 @@
         <v>45818</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31129,7 +31131,7 @@
         <v>44949</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31202,7 +31204,7 @@
         <v>45820</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31275,7 +31277,7 @@
         <v>46296</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31348,7 +31350,7 @@
         <v>45825</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31421,7 +31423,7 @@
         <v>46296</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31494,7 +31496,7 @@
         <v>46253</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31567,7 +31569,7 @@
         <v>46083</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31640,7 +31642,7 @@
         <v>45827</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31713,7 +31715,7 @@
         <v>46083</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31786,7 +31788,7 @@
         <v>46253</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31859,7 +31861,7 @@
         <v>46296</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31932,7 +31934,7 @@
         <v>46253</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32005,7 +32007,7 @@
         <v>45832</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32078,7 +32080,7 @@
         <v>46256</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32151,7 +32153,7 @@
         <v>46300</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32224,7 +32226,7 @@
         <v>46300</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32297,7 +32299,7 @@
         <v>46300</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32375,7 +32377,7 @@
         <v>45709</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32448,7 +32450,7 @@
         <v>46296</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32521,7 +32523,7 @@
         <v>45833</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32594,7 +32596,7 @@
         <v>45835</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32667,7 +32669,7 @@
         <v>45171</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32740,7 +32742,7 @@
         <v>46091</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32813,7 +32815,7 @@
         <v>45837</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32886,7 +32888,7 @@
         <v>46256</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32959,7 +32961,7 @@
         <v>46256</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33032,7 +33034,7 @@
         <v>46204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33110,7 +33112,7 @@
         <v>46254</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33183,7 +33185,7 @@
         <v>45840</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33256,7 +33258,7 @@
         <v>46092</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33329,7 +33331,7 @@
         <v>46092</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33402,7 +33404,7 @@
         <v>45832</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33475,7 +33477,7 @@
         <v>45952</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33548,7 +33550,7 @@
         <v>45030</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33621,7 +33623,7 @@
         <v>46202</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33694,7 +33696,7 @@
         <v>46097</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33767,7 +33769,7 @@
         <v>46099</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33840,7 +33842,7 @@
         <v>44510</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33913,7 +33915,7 @@
         <v>44984</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33986,7 +33988,7 @@
         <v>45820</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34059,7 +34061,7 @@
         <v>46297</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34132,7 +34134,7 @@
         <v>44598</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34205,7 +34207,7 @@
         <v>44938</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34283,7 +34285,7 @@
         <v>45483</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34356,7 +34358,7 @@
         <v>45498</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34429,7 +34431,7 @@
         <v>45811</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34502,7 +34504,7 @@
         <v>46105</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34575,7 +34577,7 @@
         <v>44879</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34648,7 +34650,7 @@
         <v>46259</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34721,7 +34723,7 @@
         <v>46301</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34794,7 +34796,7 @@
         <v>45847</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34867,7 +34869,7 @@
         <v>46101</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34940,7 +34942,7 @@
         <v>46301</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35013,7 +35015,7 @@
         <v>46301</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35086,7 +35088,7 @@
         <v>45853</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35159,7 +35161,7 @@
         <v>45755</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35232,7 +35234,7 @@
         <v>45482</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35305,7 +35307,7 @@
         <v>46111</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35378,7 +35380,7 @@
         <v>46301</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35451,7 +35453,7 @@
         <v>46112</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35524,7 +35526,7 @@
         <v>46112</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35602,7 +35604,7 @@
         <v>46112</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35680,7 +35682,7 @@
         <v>46113</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35753,7 +35755,7 @@
         <v>46113</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35826,7 +35828,7 @@
         <v>46113</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35899,7 +35901,7 @@
         <v>46112</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35977,7 +35979,7 @@
         <v>46112</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36055,7 +36057,7 @@
         <v>46112</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36133,7 +36135,7 @@
         <v>46112</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36211,7 +36213,7 @@
         <v>46113</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36284,7 +36286,7 @@
         <v>46112</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36362,7 +36364,7 @@
         <v>45769</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36435,7 +36437,7 @@
         <v>45526</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36513,7 +36515,7 @@
         <v>45867</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36586,7 +36588,7 @@
         <v>45867</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36659,7 +36661,7 @@
         <v>45618</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36732,7 +36734,7 @@
         <v>45869</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36805,7 +36807,7 @@
         <v>45870</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36878,7 +36880,7 @@
         <v>45870</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36951,7 +36953,7 @@
         <v>46303</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37024,7 +37026,7 @@
         <v>45467</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37097,7 +37099,7 @@
         <v>46303</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37170,7 +37172,7 @@
         <v>45086</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37243,7 +37245,7 @@
         <v>46121</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37316,7 +37318,7 @@
         <v>45891</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37389,7 +37391,7 @@
         <v>46125</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37462,7 +37464,7 @@
         <v>46303</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37535,7 +37537,7 @@
         <v>46303</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37608,7 +37610,7 @@
         <v>46303</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37681,7 +37683,7 @@
         <v>45880</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37759,7 +37761,7 @@
         <v>44918</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37832,7 +37834,7 @@
         <v>45880</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37905,7 +37907,7 @@
         <v>46128</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37978,7 +37980,7 @@
         <v>45378</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38051,7 +38053,7 @@
         <v>46307</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38124,7 +38126,7 @@
         <v>46307</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38197,7 +38199,7 @@
         <v>45498</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38270,7 +38272,7 @@
         <v>44893</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38343,7 +38345,7 @@
         <v>46308</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38416,7 +38418,7 @@
         <v>45275</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38489,7 +38491,7 @@
         <v>45540</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38562,7 +38564,7 @@
         <v>46308</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38635,7 +38637,7 @@
         <v>45881</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38708,7 +38710,7 @@
         <v>46136</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38781,7 +38783,7 @@
         <v>44630</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38854,7 +38856,7 @@
         <v>44893</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38927,7 +38929,7 @@
         <v>45699</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39000,7 +39002,7 @@
         <v>44994</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39073,7 +39075,7 @@
         <v>45574</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39146,7 +39148,7 @@
         <v>46307</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39219,7 +39221,7 @@
         <v>45919</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39292,7 +39294,7 @@
         <v>45224</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39370,7 +39372,7 @@
         <v>45559</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39443,7 +39445,7 @@
         <v>45804</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39516,7 +39518,7 @@
         <v>45867</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39589,7 +39591,7 @@
         <v>45867</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39662,7 +39664,7 @@
         <v>45834</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39740,7 +39742,7 @@
         <v>46307</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39813,7 +39815,7 @@
         <v>45632</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39886,7 +39888,7 @@
         <v>46308</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39959,7 +39961,7 @@
         <v>46136</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40032,7 +40034,7 @@
         <v>44587</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40105,7 +40107,7 @@
         <v>45749</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40183,7 +40185,7 @@
         <v>44935</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40256,7 +40258,7 @@
         <v>44603</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40329,7 +40331,7 @@
         <v>45825</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40402,7 +40404,7 @@
         <v>44999</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40475,7 +40477,7 @@
         <v>44999</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40548,7 +40550,7 @@
         <v>45485</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40621,7 +40623,7 @@
         <v>45924</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40694,7 +40696,7 @@
         <v>45923</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40767,7 +40769,7 @@
         <v>44964</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40840,7 +40842,7 @@
         <v>44910</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40913,7 +40915,7 @@
         <v>45517</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40986,7 +40988,7 @@
         <v>44638</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41059,7 +41061,7 @@
         <v>45658</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41132,7 +41134,7 @@
         <v>44964</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41205,7 +41207,7 @@
         <v>46267</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41278,7 +41280,7 @@
         <v>45666</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41351,7 +41353,7 @@
         <v>46272</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41424,7 +41426,7 @@
         <v>46272</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41497,7 +41499,7 @@
         <v>44832</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41570,7 +41572,7 @@
         <v>45805</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41643,7 +41645,7 @@
         <v>45001</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41716,7 +41718,7 @@
         <v>44587</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41789,7 +41791,7 @@
         <v>46271</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41862,7 +41864,7 @@
         <v>44918</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41935,7 +41937,7 @@
         <v>44959</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42008,7 +42010,7 @@
         <v>46314</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42081,7 +42083,7 @@
         <v>46314</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42154,7 +42156,7 @@
         <v>44644</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42227,7 +42229,7 @@
         <v>44966</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42300,7 +42302,7 @@
         <v>45495</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42373,7 +42375,7 @@
         <v>44600</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42446,7 +42448,7 @@
         <v>45954</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42519,7 +42521,7 @@
         <v>45026</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42592,7 +42594,7 @@
         <v>44910</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42665,7 +42667,7 @@
         <v>45567</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42738,7 +42740,7 @@
         <v>45554</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42811,7 +42813,7 @@
         <v>45992</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42884,7 +42886,7 @@
         <v>45875</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42957,7 +42959,7 @@
         <v>45875</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43030,7 +43032,7 @@
         <v>46316</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43103,7 +43105,7 @@
         <v>45768</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43176,7 +43178,7 @@
         <v>45567</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43249,7 +43251,7 @@
         <v>45791</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43322,7 +43324,7 @@
         <v>46316</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43395,7 +43397,7 @@
         <v>45145</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43468,7 +43470,7 @@
         <v>46315</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43541,7 +43543,7 @@
         <v>46275</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43614,7 +43616,7 @@
         <v>46276</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43687,7 +43689,7 @@
         <v>46272</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43760,7 +43762,7 @@
         <v>45202</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43833,7 +43835,7 @@
         <v>46275</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43906,7 +43908,7 @@
         <v>46272</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43979,7 +43981,7 @@
         <v>46274</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44052,7 +44054,7 @@
         <v>46318</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44125,7 +44127,7 @@
         <v>46274</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44198,7 +44200,7 @@
         <v>46276</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44271,7 +44273,7 @@
         <v>44943</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44344,7 +44346,7 @@
         <v>44944</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44417,7 +44419,7 @@
         <v>46272</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44490,7 +44492,7 @@
         <v>46272</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44563,7 +44565,7 @@
         <v>45394</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44636,7 +44638,7 @@
         <v>46275</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44709,7 +44711,7 @@
         <v>46276</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44782,7 +44784,7 @@
         <v>46275</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44855,7 +44857,7 @@
         <v>44867</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44928,7 +44930,7 @@
         <v>45581</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45001,7 +45003,7 @@
         <v>45533</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45079,7 +45081,7 @@
         <v>45588</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45152,7 +45154,7 @@
         <v>44784</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45225,7 +45227,7 @@
         <v>45176</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45298,7 +45300,7 @@
         <v>46150</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45371,7 +45373,7 @@
         <v>45569</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45444,7 +45446,7 @@
         <v>44999</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45517,7 +45519,7 @@
         <v>45170</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45590,7 +45592,7 @@
         <v>44746</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45663,7 +45665,7 @@
         <v>45622</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45736,7 +45738,7 @@
         <v>45562</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45809,7 +45811,7 @@
         <v>45075</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45882,7 +45884,7 @@
         <v>44784</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45955,7 +45957,7 @@
         <v>45343</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46028,7 +46030,7 @@
         <v>46104</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46101,7 +46103,7 @@
         <v>45981</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46174,7 +46176,7 @@
         <v>45867</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46247,7 +46249,7 @@
         <v>45121</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46325,7 +46327,7 @@
         <v>45755</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46398,7 +46400,7 @@
         <v>45617</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46471,7 +46473,7 @@
         <v>44981</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46544,7 +46546,7 @@
         <v>44994</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46617,7 +46619,7 @@
         <v>44958</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46690,7 +46692,7 @@
         <v>44965</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46763,7 +46765,7 @@
         <v>45334</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46836,7 +46838,7 @@
         <v>44973</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46909,7 +46911,7 @@
         <v>44977</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46982,7 +46984,7 @@
         <v>45610</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47055,7 +47057,7 @@
         <v>44894</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47128,7 +47130,7 @@
         <v>44992</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47201,7 +47203,7 @@
         <v>45020</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47274,7 +47276,7 @@
         <v>45114</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47347,7 +47349,7 @@
         <v>45041</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47420,7 +47422,7 @@
         <v>45632</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47493,7 +47495,7 @@
         <v>44745</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47566,7 +47568,7 @@
         <v>45615</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47639,7 +47641,7 @@
         <v>45635</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47712,7 +47714,7 @@
         <v>45568</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47785,7 +47787,7 @@
         <v>45033</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47858,7 +47860,7 @@
         <v>45699</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47931,7 +47933,7 @@
         <v>45154</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48004,7 +48006,7 @@
         <v>45630</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48077,7 +48079,7 @@
         <v>45189</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48150,7 +48152,7 @@
         <v>45063</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48223,7 +48225,7 @@
         <v>44769</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48296,7 +48298,7 @@
         <v>44546</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48369,7 +48371,7 @@
         <v>45646</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -48442,7 +48444,7 @@
         <v>44988</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48515,7 +48517,7 @@
         <v>45121</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48588,7 +48590,7 @@
         <v>44502</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48661,7 +48663,7 @@
         <v>45732</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48734,7 +48736,7 @@
         <v>45090</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48807,7 +48809,7 @@
         <v>45090</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48880,7 +48882,7 @@
         <v>45201</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48953,7 +48955,7 @@
         <v>44991</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49026,7 +49028,7 @@
         <v>45113</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49099,7 +49101,7 @@
         <v>45238</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49172,7 +49174,7 @@
         <v>45063</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49245,7 +49247,7 @@
         <v>45219</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49318,7 +49320,7 @@
         <v>45754</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -49391,7 +49393,7 @@
         <v>45114</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -49464,7 +49466,7 @@
         <v>45482</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49537,7 +49539,7 @@
         <v>45482</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49610,7 +49612,7 @@
         <v>45533</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49683,7 +49685,7 @@
         <v>45732</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49756,7 +49758,7 @@
         <v>45111</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49829,7 +49831,7 @@
         <v>44910</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49902,7 +49904,7 @@
         <v>44598</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49975,7 +49977,7 @@
         <v>44931</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50053,7 +50055,7 @@
         <v>45027</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50131,7 +50133,7 @@
         <v>45112</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50204,7 +50206,7 @@
         <v>45029</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50277,7 +50279,7 @@
         <v>45346</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -50350,7 +50352,7 @@
         <v>44966</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -50423,7 +50425,7 @@
         <v>44903</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50496,7 +50498,7 @@
         <v>44578</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50569,7 +50571,7 @@
         <v>44867</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50642,7 +50644,7 @@
         <v>44879</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50715,7 +50717,7 @@
         <v>44903</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50788,7 +50790,7 @@
         <v>44896</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50861,7 +50863,7 @@
         <v>44890</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50934,7 +50936,7 @@
         <v>44588</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51007,7 +51009,7 @@
         <v>44588</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51080,7 +51082,7 @@
         <v>45361</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51153,7 +51155,7 @@
         <v>45224</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51231,7 +51233,7 @@
         <v>44754</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51304,7 +51306,7 @@
         <v>45100</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -51377,7 +51379,7 @@
         <v>44517</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -51450,7 +51452,7 @@
         <v>45110</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51523,7 +51525,7 @@
         <v>45196</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51596,7 +51598,7 @@
         <v>44607</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51669,7 +51671,7 @@
         <v>44949</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51747,7 +51749,7 @@
         <v>45121</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51825,7 +51827,7 @@
         <v>45569</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51898,7 +51900,7 @@
         <v>45391</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51971,7 +51973,7 @@
         <v>45086</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52044,7 +52046,7 @@
         <v>45086</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52117,7 +52119,7 @@
         <v>45086</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52190,7 +52192,7 @@
         <v>44720</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52263,7 +52265,7 @@
         <v>44539</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -52336,7 +52338,7 @@
         <v>44553</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -52409,7 +52411,7 @@
         <v>44964</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52482,7 +52484,7 @@
         <v>44867</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52555,7 +52557,7 @@
         <v>45096</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52628,7 +52630,7 @@
         <v>45111</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52701,7 +52703,7 @@
         <v>45588</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52774,7 +52776,7 @@
         <v>44967</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52847,7 +52849,7 @@
         <v>45581</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52920,7 +52922,7 @@
         <v>45481</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52993,7 +52995,7 @@
         <v>45539</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53066,7 +53068,7 @@
         <v>45539</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53139,7 +53141,7 @@
         <v>45000</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53212,7 +53214,7 @@
         <v>45552</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -53285,7 +53287,7 @@
         <v>45098</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -53358,7 +53360,7 @@
         <v>45113</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -53431,7 +53433,7 @@
         <v>44788</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53504,7 +53506,7 @@
         <v>45581</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53577,7 +53579,7 @@
         <v>45548</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53650,7 +53652,7 @@
         <v>45020</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53723,7 +53725,7 @@
         <v>45569</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53796,7 +53798,7 @@
         <v>45415</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53869,7 +53871,7 @@
         <v>45009</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53942,7 +53944,7 @@
         <v>45111</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54015,7 +54017,7 @@
         <v>45111</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54088,7 +54090,7 @@
         <v>45621</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54161,7 +54163,7 @@
         <v>45114</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -54234,7 +54236,7 @@
         <v>45460</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -54307,7 +54309,7 @@
         <v>45533</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -54385,7 +54387,7 @@
         <v>45741</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -54458,7 +54460,7 @@
         <v>45552</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54531,7 +54533,7 @@
         <v>45271</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54604,7 +54606,7 @@
         <v>44585</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54677,7 +54679,7 @@
         <v>45572</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54750,7 +54752,7 @@
         <v>45001</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54823,7 +54825,7 @@
         <v>45182</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54896,7 +54898,7 @@
         <v>45377</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54969,7 +54971,7 @@
         <v>44579</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55042,7 +55044,7 @@
         <v>44643</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55115,7 +55117,7 @@
         <v>45328</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55188,7 +55190,7 @@
         <v>45713</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -55261,7 +55263,7 @@
         <v>45071</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -55334,7 +55336,7 @@
         <v>44795</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -55407,7 +55409,7 @@
         <v>45168</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55480,7 +55482,7 @@
         <v>45052</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55553,7 +55555,7 @@
         <v>45623</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55626,7 +55628,7 @@
         <v>44635</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55699,7 +55701,7 @@
         <v>45211</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55772,7 +55774,7 @@
         <v>45211</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55845,7 +55847,7 @@
         <v>45650</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55918,7 +55920,7 @@
         <v>45195</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55991,7 +55993,7 @@
         <v>45351</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56064,7 +56066,7 @@
         <v>45208</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56137,7 +56139,7 @@
         <v>45148</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -56210,7 +56212,7 @@
         <v>45148</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -56283,7 +56285,7 @@
         <v>45163</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -56356,7 +56358,7 @@
         <v>45079</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -56429,7 +56431,7 @@
         <v>45254</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56507,7 +56509,7 @@
         <v>45113</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56580,7 +56582,7 @@
         <v>44825</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56653,7 +56655,7 @@
         <v>45128</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56726,7 +56728,7 @@
         <v>45196</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56799,7 +56801,7 @@
         <v>45236</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56872,7 +56874,7 @@
         <v>44663</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56945,7 +56947,7 @@
         <v>45187</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57018,7 +57020,7 @@
         <v>45187</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57091,7 +57093,7 @@
         <v>45707</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -57164,7 +57166,7 @@
         <v>45308</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -57237,7 +57239,7 @@
         <v>45699</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -57310,7 +57312,7 @@
         <v>45174</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -57383,7 +57385,7 @@
         <v>45722</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -57456,7 +57458,7 @@
         <v>45761</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57529,7 +57531,7 @@
         <v>45299</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57602,7 +57604,7 @@
         <v>45700</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57675,7 +57677,7 @@
         <v>45623</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57748,7 +57750,7 @@
         <v>44790</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57821,7 +57823,7 @@
         <v>45260</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57894,7 +57896,7 @@
         <v>44820</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57967,7 +57969,7 @@
         <v>44693</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58045,7 +58047,7 @@
         <v>45245</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -58118,7 +58120,7 @@
         <v>45280</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -58191,7 +58193,7 @@
         <v>44956</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -58269,7 +58271,7 @@
         <v>45317</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -58347,7 +58349,7 @@
         <v>45219</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -58420,7 +58422,7 @@
         <v>45225</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -58493,7 +58495,7 @@
         <v>45237</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58566,7 +58568,7 @@
         <v>45237</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58639,7 +58641,7 @@
         <v>44732</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58712,7 +58714,7 @@
         <v>44790</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58785,7 +58787,7 @@
         <v>45323</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58858,7 +58860,7 @@
         <v>45533</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58931,7 +58933,7 @@
         <v>45355</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59004,7 +59006,7 @@
         <v>45361</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59077,7 +59079,7 @@
         <v>45330</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -59150,7 +59152,7 @@
         <v>44839</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -59223,7 +59225,7 @@
         <v>45217</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -59296,7 +59298,7 @@
         <v>44578</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -59369,7 +59371,7 @@
         <v>44897</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -59442,7 +59444,7 @@
         <v>45091</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59515,7 +59517,7 @@
         <v>45259</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59593,7 +59595,7 @@
         <v>45259</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59671,7 +59673,7 @@
         <v>45349</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59744,7 +59746,7 @@
         <v>44599</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59817,7 +59819,7 @@
         <v>45201</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59890,7 +59892,7 @@
         <v>45674</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59963,7 +59965,7 @@
         <v>45588</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60036,7 +60038,7 @@
         <v>45275</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -60109,7 +60111,7 @@
         <v>44495</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -60182,7 +60184,7 @@
         <v>44848</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -60255,7 +60257,7 @@
         <v>45440</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -60328,7 +60330,7 @@
         <v>44790</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -60401,7 +60403,7 @@
         <v>44861</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -60474,7 +60476,7 @@
         <v>44879</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60547,7 +60549,7 @@
         <v>45147</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60620,7 +60622,7 @@
         <v>44987</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60693,7 +60695,7 @@
         <v>45128</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60766,7 +60768,7 @@
         <v>45481</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60839,7 +60841,7 @@
         <v>44900</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60912,7 +60914,7 @@
         <v>45394</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60985,7 +60987,7 @@
         <v>44857</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -61058,7 +61060,7 @@
         <v>44585</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -61131,7 +61133,7 @@
         <v>44542</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -61204,7 +61206,7 @@
         <v>44566</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -61277,7 +61279,7 @@
         <v>45743</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -61350,7 +61352,7 @@
         <v>45261</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -61423,7 +61425,7 @@
         <v>45048</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61496,7 +61498,7 @@
         <v>45503</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61569,7 +61571,7 @@
         <v>44596</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61642,7 +61644,7 @@
         <v>44952</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61715,7 +61717,7 @@
         <v>45215</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61788,7 +61790,7 @@
         <v>44992</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61861,7 +61863,7 @@
         <v>44237</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61934,7 +61936,7 @@
         <v>44587</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -62007,7 +62009,7 @@
         <v>44603</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -62080,7 +62082,7 @@
         <v>44610</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -62153,7 +62155,7 @@
         <v>44602</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -62226,7 +62228,7 @@
         <v>44981</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -62304,7 +62306,7 @@
         <v>45351</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -62377,7 +62379,7 @@
         <v>44992</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -62450,7 +62452,7 @@
         <v>45224</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62523,7 +62525,7 @@
         <v>45415</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62596,7 +62598,7 @@
         <v>45378</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62674,7 +62676,7 @@
         <v>45488</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62747,7 +62749,7 @@
         <v>45488</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62820,7 +62822,7 @@
         <v>45114</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62893,7 +62895,7 @@
         <v>45488</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62966,7 +62968,7 @@
         <v>45484</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -63039,7 +63041,7 @@
         <v>45484</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -63112,7 +63114,7 @@
         <v>44853</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -63185,7 +63187,7 @@
         <v>45761</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -63263,7 +63265,7 @@
         <v>45832</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -63336,7 +63338,7 @@
         <v>45840</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -63409,7 +63411,7 @@
         <v>45840</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -63482,7 +63484,7 @@
         <v>45840</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63555,7 +63557,7 @@
         <v>45845</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63628,7 +63630,7 @@
         <v>45848</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63701,7 +63703,7 @@
         <v>45884</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -63779,7 +63781,7 @@
         <v>45978</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -63852,7 +63854,7 @@
         <v>46065</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -63925,7 +63927,7 @@
         <v>46154</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -63998,7 +64000,7 @@
         <v>46154</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -64071,7 +64073,7 @@
         <v>46169</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -64144,7 +64146,7 @@
         <v>46198</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -64222,7 +64224,7 @@
         <v>46153</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -64315,7 +64317,7 @@
         <v>46293</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -64388,7 +64390,7 @@
         <v>46293</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
